--- a/Roy_Okola_Scholarship_Database_LATEST.xlsx
+++ b/Roy_Okola_Scholarship_Database_LATEST.xlsx
@@ -1174,87 +1174,87 @@
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="38">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Scholarship</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Programme</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>University</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="45" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="45" t="inlineStr">
         <is>
           <t>Funding</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="45" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="J2" s="44" t="inlineStr">
+      <c r="J2" s="45" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="K2" s="45" t="inlineStr">
         <is>
           <t>Elig.</t>
         </is>
       </c>
-      <c r="L2" s="44" t="inlineStr">
+      <c r="L2" s="45" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="M2" s="44" t="inlineStr">
+      <c r="M2" s="45" t="inlineStr">
         <is>
           <t>Competitiveness</t>
         </is>
       </c>
-      <c r="N2" s="44" t="inlineStr">
+      <c r="N2" s="45" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="O2" s="44" t="inlineStr">
+      <c r="O2" s="45" t="inlineStr">
         <is>
           <t>Roy Eligible?</t>
         </is>
       </c>
-      <c r="P2" s="44" t="inlineStr">
+      <c r="P2" s="45" t="inlineStr">
         <is>
           <t>Notes / Action</t>
         </is>
       </c>
-      <c r="Q2" s="44" t="inlineStr">
+      <c r="Q2" s="45" t="inlineStr">
         <is>
           <t>Official Link</t>
         </is>
@@ -1638,87 +1638,87 @@
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="38">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Scholarship</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Programme</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>University</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="45" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="45" t="inlineStr">
         <is>
           <t>Funding</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="45" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="J2" s="44" t="inlineStr">
+      <c r="J2" s="45" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="K2" s="45" t="inlineStr">
         <is>
           <t>Elig.</t>
         </is>
       </c>
-      <c r="L2" s="44" t="inlineStr">
+      <c r="L2" s="45" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="M2" s="44" t="inlineStr">
+      <c r="M2" s="45" t="inlineStr">
         <is>
           <t>Competitiveness</t>
         </is>
       </c>
-      <c r="N2" s="44" t="inlineStr">
+      <c r="N2" s="45" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="O2" s="44" t="inlineStr">
+      <c r="O2" s="45" t="inlineStr">
         <is>
           <t>Roy Eligible?</t>
         </is>
       </c>
-      <c r="P2" s="44" t="inlineStr">
+      <c r="P2" s="45" t="inlineStr">
         <is>
           <t>Notes / Action</t>
         </is>
       </c>
-      <c r="Q2" s="44" t="inlineStr">
+      <c r="Q2" s="45" t="inlineStr">
         <is>
           <t>Official Link</t>
         </is>
@@ -2102,87 +2102,87 @@
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="38">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Scholarship</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Programme</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>University</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="45" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="45" t="inlineStr">
         <is>
           <t>Funding</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="45" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="J2" s="44" t="inlineStr">
+      <c r="J2" s="45" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="K2" s="45" t="inlineStr">
         <is>
           <t>Elig.</t>
         </is>
       </c>
-      <c r="L2" s="44" t="inlineStr">
+      <c r="L2" s="45" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="M2" s="44" t="inlineStr">
+      <c r="M2" s="45" t="inlineStr">
         <is>
           <t>Competitiveness</t>
         </is>
       </c>
-      <c r="N2" s="44" t="inlineStr">
+      <c r="N2" s="45" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="O2" s="44" t="inlineStr">
+      <c r="O2" s="45" t="inlineStr">
         <is>
           <t>Roy Eligible?</t>
         </is>
       </c>
-      <c r="P2" s="44" t="inlineStr">
+      <c r="P2" s="45" t="inlineStr">
         <is>
           <t>Notes / Action</t>
         </is>
       </c>
-      <c r="Q2" s="44" t="inlineStr">
+      <c r="Q2" s="45" t="inlineStr">
         <is>
           <t>Official Link</t>
         </is>
@@ -2649,87 +2649,87 @@
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="38">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Scholarship</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Programme</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>University</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="45" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="45" t="inlineStr">
         <is>
           <t>Funding</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="45" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="J2" s="44" t="inlineStr">
+      <c r="J2" s="45" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="K2" s="45" t="inlineStr">
         <is>
           <t>Elig.</t>
         </is>
       </c>
-      <c r="L2" s="44" t="inlineStr">
+      <c r="L2" s="45" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="M2" s="44" t="inlineStr">
+      <c r="M2" s="45" t="inlineStr">
         <is>
           <t>Competitiveness</t>
         </is>
       </c>
-      <c r="N2" s="44" t="inlineStr">
+      <c r="N2" s="45" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="O2" s="44" t="inlineStr">
+      <c r="O2" s="45" t="inlineStr">
         <is>
           <t>Roy Eligible?</t>
         </is>
       </c>
-      <c r="P2" s="44" t="inlineStr">
+      <c r="P2" s="45" t="inlineStr">
         <is>
           <t>Notes / Action</t>
         </is>
       </c>
-      <c r="Q2" s="44" t="inlineStr">
+      <c r="Q2" s="45" t="inlineStr">
         <is>
           <t>Official Link</t>
         </is>
@@ -3772,67 +3772,67 @@
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="38">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>Scholarship</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>Elig.</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="45" t="inlineStr">
         <is>
           <t>Days Left</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="45" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="45" t="inlineStr">
         <is>
           <t>Next Action Due</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="45" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="J2" s="44" t="inlineStr">
+      <c r="J2" s="45" t="inlineStr">
         <is>
           <t>RefLtrs</t>
         </is>
       </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="K2" s="45" t="inlineStr">
         <is>
           <t>Transcripts</t>
         </is>
       </c>
-      <c r="L2" s="44" t="inlineStr">
+      <c r="L2" s="45" t="inlineStr">
         <is>
           <t>MOI</t>
         </is>
       </c>
-      <c r="M2" s="44" t="inlineStr">
+      <c r="M2" s="45" t="inlineStr">
         <is>
           <t>Notes/Risk</t>
         </is>
@@ -4610,32 +4610,32 @@
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="38">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Record/Sheet</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Change Type</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>Previous Value</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>New Value</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="45" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -5584,27 +5584,27 @@
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="38">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>Notes / Action</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>Needed By</t>
         </is>
@@ -6248,47 +6248,47 @@
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="38">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Scholarship</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>Elig.</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="45" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="45" t="inlineStr">
         <is>
           <t>Funding Detail</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="45" t="inlineStr">
         <is>
           <t>English Req.</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="45" t="inlineStr">
         <is>
           <t>MBA Impact?</t>
         </is>
@@ -8204,7 +8204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:R81"/>
+  <dimension ref="A1:R145"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="37" min="1" max="1"/>
@@ -8228,92 +8228,92 @@
     <row r="1" ht="21.75" customHeight="1" s="38">
       <c r="A1" s="39" t="inlineStr">
         <is>
-          <t>ROY OKOLA OTIENO — MASTER DATABASE v3 (Cycle 2 Weekly Sync)  |  12 Aug 2026  |  41 Roy Priority + 38 Global = 79 total records</t>
+          <t>ROY OKOLA OTIENO — MASTER DATABASE v3 (Cycle 2 Weekly Sync)  |  12 Aug 2026  |  41 Roy Priority + 102 Global = 143 total records</t>
         </is>
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="38">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Scholarship</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Programme</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>University</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="45" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="45" t="inlineStr">
         <is>
           <t>Funding</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="45" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="J2" s="44" t="inlineStr">
+      <c r="J2" s="45" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="K2" s="45" t="inlineStr">
         <is>
           <t>Elig.</t>
         </is>
       </c>
-      <c r="L2" s="44" t="inlineStr">
+      <c r="L2" s="45" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="M2" s="44" t="inlineStr">
+      <c r="M2" s="45" t="inlineStr">
         <is>
           <t>Competitiveness</t>
         </is>
       </c>
-      <c r="N2" s="44" t="inlineStr">
+      <c r="N2" s="45" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="O2" s="44" t="inlineStr">
+      <c r="O2" s="45" t="inlineStr">
         <is>
           <t>Roy Eligible?</t>
         </is>
       </c>
-      <c r="P2" s="44" t="inlineStr">
+      <c r="P2" s="45" t="inlineStr">
         <is>
           <t>Notes / Action</t>
         </is>
       </c>
-      <c r="Q2" s="44" t="inlineStr">
+      <c r="Q2" s="45" t="inlineStr">
         <is>
           <t>Official Link</t>
         </is>
@@ -15273,6 +15273,5638 @@
       <c r="R81" s="65" t="inlineStr">
         <is>
           <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="64" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="64" t="inlineStr">
+        <is>
+          <t>Heinrich Boll Foundation Scholarship</t>
+        </is>
+      </c>
+      <c r="C82" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD (all fields, green/feminist focus)</t>
+        </is>
+      </c>
+      <c r="D82" s="64" t="inlineStr">
+        <is>
+          <t>Various German &amp; international universities</t>
+        </is>
+      </c>
+      <c r="E82" s="64" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F82" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G82" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H82" s="64" t="inlineStr">
+        <is>
+          <t>Full: monthly stipend EUR 850 (masters) / EUR 1,200 (PhD) + project allowance</t>
+        </is>
+      </c>
+      <c r="I82" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J82" s="64" t="inlineStr">
+        <is>
+          <t>German B2+ or English depending on programme</t>
+        </is>
+      </c>
+      <c r="K82" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L82" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="64" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="N82" s="64" t="inlineStr">
+        <is>
+          <t>Politics / Environment / Social Sciences</t>
+        </is>
+      </c>
+      <c r="O82" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P82" s="64" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa eligible; strong civil society and political engagement expected; apply via HBS country office</t>
+        </is>
+      </c>
+      <c r="Q82" s="64" t="inlineStr">
+        <is>
+          <t>https://www.boell.de/en/foundation/scholarships</t>
+        </is>
+      </c>
+      <c r="R82" s="65" t="inlineStr">
+        <is>
+          <t>Global - Social Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="64" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="64" t="inlineStr">
+        <is>
+          <t>Friedrich Ebert Stiftung (FES) Scholarship</t>
+        </is>
+      </c>
+      <c r="C83" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD (social sciences, economics, law, politics)</t>
+        </is>
+      </c>
+      <c r="D83" s="64" t="inlineStr">
+        <is>
+          <t>Various German &amp; international universities</t>
+        </is>
+      </c>
+      <c r="E83" s="64" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F83" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G83" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H83" s="64" t="inlineStr">
+        <is>
+          <t>Full: monthly stipend + health insurance + project allowance</t>
+        </is>
+      </c>
+      <c r="I83" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J83" s="64" t="inlineStr">
+        <is>
+          <t>German B2+ or English</t>
+        </is>
+      </c>
+      <c r="K83" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L83" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N83" s="64" t="inlineStr">
+        <is>
+          <t>Social Sciences / Economics / Law</t>
+        </is>
+      </c>
+      <c r="O83" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P83" s="64" t="inlineStr">
+        <is>
+          <t>Focus on social democracy, trade unions, development; apply via FES country office in Kenya</t>
+        </is>
+      </c>
+      <c r="Q83" s="64" t="inlineStr">
+        <is>
+          <t>https://www.fes.de/en/scholarships</t>
+        </is>
+      </c>
+      <c r="R83" s="65" t="inlineStr">
+        <is>
+          <t>Global - Social Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="64" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="64" t="inlineStr">
+        <is>
+          <t>Konrad Adenauer Stiftung (KAS) Scholarship</t>
+        </is>
+      </c>
+      <c r="C84" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD (all fields, Christian democratic values)</t>
+        </is>
+      </c>
+      <c r="D84" s="64" t="inlineStr">
+        <is>
+          <t>Various German &amp; international universities</t>
+        </is>
+      </c>
+      <c r="E84" s="64" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F84" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G84" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H84" s="64" t="inlineStr">
+        <is>
+          <t>Full: monthly stipend + health insurance + language course</t>
+        </is>
+      </c>
+      <c r="I84" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J84" s="64" t="inlineStr">
+        <is>
+          <t>German B2+ or English</t>
+        </is>
+      </c>
+      <c r="K84" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L84" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N84" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O84" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P84" s="64" t="inlineStr">
+        <is>
+          <t>Africa programme active; Kenya eligible; academic excellence + civic engagement required; apply via KAS Nairobi</t>
+        </is>
+      </c>
+      <c r="Q84" s="64" t="inlineStr">
+        <is>
+          <t>https://www.kas.de/en/web/begabtenfoerderung-und-kultur/scholarships</t>
+        </is>
+      </c>
+      <c r="R84" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="64" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="64" t="inlineStr">
+        <is>
+          <t>Friedrich Naumann Foundation Scholarship</t>
+        </is>
+      </c>
+      <c r="C85" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD (liberal political thought, economics, law)</t>
+        </is>
+      </c>
+      <c r="D85" s="64" t="inlineStr">
+        <is>
+          <t>Various German &amp; international universities</t>
+        </is>
+      </c>
+      <c r="E85" s="64" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F85" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G85" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H85" s="64" t="inlineStr">
+        <is>
+          <t>Full: monthly stipend + health insurance</t>
+        </is>
+      </c>
+      <c r="I85" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J85" s="64" t="inlineStr">
+        <is>
+          <t>German B2+ or English</t>
+        </is>
+      </c>
+      <c r="K85" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L85" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N85" s="64" t="inlineStr">
+        <is>
+          <t>Economics / Law / Political Sciences</t>
+        </is>
+      </c>
+      <c r="O85" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P85" s="64" t="inlineStr">
+        <is>
+          <t>Liberal values focus; Kenya eligible; apply via FNF East Africa office</t>
+        </is>
+      </c>
+      <c r="Q85" s="64" t="inlineStr">
+        <is>
+          <t>https://www.freiheit.org/scholarships</t>
+        </is>
+      </c>
+      <c r="R85" s="65" t="inlineStr">
+        <is>
+          <t>Global - Social Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="64" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="64" t="inlineStr">
+        <is>
+          <t>Hanns Seidel Stiftung Scholarship</t>
+        </is>
+      </c>
+      <c r="C86" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD (all fields)</t>
+        </is>
+      </c>
+      <c r="D86" s="64" t="inlineStr">
+        <is>
+          <t>Various German universities</t>
+        </is>
+      </c>
+      <c r="E86" s="64" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F86" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G86" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H86" s="64" t="inlineStr">
+        <is>
+          <t>Full: monthly stipend + health insurance + seminar costs</t>
+        </is>
+      </c>
+      <c r="I86" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J86" s="64" t="inlineStr">
+        <is>
+          <t>German B2+ required</t>
+        </is>
+      </c>
+      <c r="K86" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L86" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N86" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O86" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P86" s="64" t="inlineStr">
+        <is>
+          <t>German language requirement limits accessibility; Bavaria-based CSU values</t>
+        </is>
+      </c>
+      <c r="Q86" s="64" t="inlineStr">
+        <is>
+          <t>https://www.hss.de/en/education/scholarships/</t>
+        </is>
+      </c>
+      <c r="R86" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="64" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="64" t="inlineStr">
+        <is>
+          <t>Rosa Luxemburg Stiftung Scholarship</t>
+        </is>
+      </c>
+      <c r="C87" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD (humanities, social sciences, arts, left-wing focus)</t>
+        </is>
+      </c>
+      <c r="D87" s="64" t="inlineStr">
+        <is>
+          <t>Various German &amp; international universities</t>
+        </is>
+      </c>
+      <c r="E87" s="64" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F87" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G87" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H87" s="64" t="inlineStr">
+        <is>
+          <t>Full: monthly stipend + health insurance</t>
+        </is>
+      </c>
+      <c r="I87" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J87" s="64" t="inlineStr">
+        <is>
+          <t>German B2+ or English</t>
+        </is>
+      </c>
+      <c r="K87" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L87" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N87" s="64" t="inlineStr">
+        <is>
+          <t>Humanities / Social Sciences</t>
+        </is>
+      </c>
+      <c r="O87" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P87" s="64" t="inlineStr">
+        <is>
+          <t>Progressive / socialist values focus; international scholarship programme open to Kenya</t>
+        </is>
+      </c>
+      <c r="Q87" s="64" t="inlineStr">
+        <is>
+          <t>https://www.rosalux.de/en/foundation/scholarships</t>
+        </is>
+      </c>
+      <c r="R87" s="65" t="inlineStr">
+        <is>
+          <t>Global - Social Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="64" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="64" t="inlineStr">
+        <is>
+          <t>KAAD (Catholic Academic Exchange Service) Scholarship</t>
+        </is>
+      </c>
+      <c r="C88" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD (all fields, Catholic values)</t>
+        </is>
+      </c>
+      <c r="D88" s="64" t="inlineStr">
+        <is>
+          <t>Various German &amp; international universities</t>
+        </is>
+      </c>
+      <c r="E88" s="64" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F88" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G88" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H88" s="64" t="inlineStr">
+        <is>
+          <t>Full: monthly stipend + health insurance + seminar costs</t>
+        </is>
+      </c>
+      <c r="I88" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J88" s="64" t="inlineStr">
+        <is>
+          <t>German B2+ or English</t>
+        </is>
+      </c>
+      <c r="K88" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L88" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N88" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O88" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P88" s="64" t="inlineStr">
+        <is>
+          <t>For Catholic students from developing countries including Kenya; pastoral accompaniment required</t>
+        </is>
+      </c>
+      <c r="Q88" s="64" t="inlineStr">
+        <is>
+          <t>https://www.kaad.de/en/funding/scholarships/</t>
+        </is>
+      </c>
+      <c r="R88" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="64" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="64" t="inlineStr">
+        <is>
+          <t>Alexander von Humboldt Foundation Research Fellowship</t>
+        </is>
+      </c>
+      <c r="C89" s="64" t="inlineStr">
+        <is>
+          <t>Postdoctoral research fellowship (6-24 months)</t>
+        </is>
+      </c>
+      <c r="D89" s="64" t="inlineStr">
+        <is>
+          <t>Various German research institutions</t>
+        </is>
+      </c>
+      <c r="E89" s="64" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F89" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G89" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H89" s="64" t="inlineStr">
+        <is>
+          <t>Full: monthly stipend EUR 2,670 + travel + family allowance</t>
+        </is>
+      </c>
+      <c r="I89" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J89" s="64" t="inlineStr">
+        <is>
+          <t>English or German</t>
+        </is>
+      </c>
+      <c r="K89" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L89" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="64" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="N89" s="64" t="inlineStr">
+        <is>
+          <t>Sciences / Engineering / Humanities</t>
+        </is>
+      </c>
+      <c r="O89" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P89" s="64" t="inlineStr">
+        <is>
+          <t>For postdoctoral researchers; not a taught masters -- listed for PhD/postdoc awareness; extremely competitive</t>
+        </is>
+      </c>
+      <c r="Q89" s="64" t="inlineStr">
+        <is>
+          <t>https://www.humboldt-foundation.de</t>
+        </is>
+      </c>
+      <c r="R89" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="64" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="64" t="inlineStr">
+        <is>
+          <t>World Bank / JJ-WBGSP Scholarship</t>
+        </is>
+      </c>
+      <c r="C90" s="64" t="inlineStr">
+        <is>
+          <t>Masters in development-related fields at selected universities</t>
+        </is>
+      </c>
+      <c r="D90" s="64" t="inlineStr">
+        <is>
+          <t>Selected universities worldwide including Africa</t>
+        </is>
+      </c>
+      <c r="E90" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F90" s="64" t="inlineStr">
+        <is>
+          <t>2027-04-15</t>
+        </is>
+      </c>
+      <c r="G90" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 246 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H90" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + living allowance + travel + health insurance</t>
+        </is>
+      </c>
+      <c r="I90" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J90" s="64" t="inlineStr">
+        <is>
+          <t>English proficiency (institution standard)</t>
+        </is>
+      </c>
+      <c r="K90" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L90" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N90" s="64" t="inlineStr">
+        <is>
+          <t>Development / Economics / Agriculture / Environment</t>
+        </is>
+      </c>
+      <c r="O90" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P90" s="64" t="inlineStr">
+        <is>
+          <t>Must be national of World Bank borrowing country (Kenya eligible); must intend to return; apply after admission offer from partner university</t>
+        </is>
+      </c>
+      <c r="Q90" s="64" t="inlineStr">
+        <is>
+          <t>https://www.worldbank.org/en/programs/scholarships</t>
+        </is>
+      </c>
+      <c r="R90" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="64" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="64" t="inlineStr">
+        <is>
+          <t>United Nations University (UNU) Fellowships</t>
+        </is>
+      </c>
+      <c r="C91" s="64" t="inlineStr">
+        <is>
+          <t>Masters or research programmes at UNU institutes</t>
+        </is>
+      </c>
+      <c r="D91" s="64" t="inlineStr">
+        <is>
+          <t>UNU institutes (Tokyo, Bonn, Bruges, Accra, etc.)</t>
+        </is>
+      </c>
+      <c r="E91" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F91" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G91" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H91" s="64" t="inlineStr">
+        <is>
+          <t>Full or partial (varies by programme)</t>
+        </is>
+      </c>
+      <c r="I91" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J91" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K91" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L91" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N91" s="64" t="inlineStr">
+        <is>
+          <t>Sustainability / Governance / Technology / Environment</t>
+        </is>
+      </c>
+      <c r="O91" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P91" s="64" t="inlineStr">
+        <is>
+          <t>UNU-INRA in Ghana runs Africa-focused programmes; check UNU website for open calls</t>
+        </is>
+      </c>
+      <c r="Q91" s="64" t="inlineStr">
+        <is>
+          <t>https://unu.edu/study</t>
+        </is>
+      </c>
+      <c r="R91" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="64" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="64" t="inlineStr">
+        <is>
+          <t>African Development Bank (AfDB) – Japanese Trust Fund Scholarship</t>
+        </is>
+      </c>
+      <c r="C92" s="64" t="inlineStr">
+        <is>
+          <t>Masters in development-related fields at Japanese universities</t>
+        </is>
+      </c>
+      <c r="D92" s="64" t="inlineStr">
+        <is>
+          <t>University of Tsukuba, GRIPS, JICA partner universities</t>
+        </is>
+      </c>
+      <c r="E92" s="64" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F92" s="64" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="G92" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 156 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H92" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + stipend + accommodation + flights</t>
+        </is>
+      </c>
+      <c r="I92" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J92" s="64" t="inlineStr">
+        <is>
+          <t>English TOEFL 550+ or IELTS 6.0+</t>
+        </is>
+      </c>
+      <c r="K92" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L92" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N92" s="64" t="inlineStr">
+        <is>
+          <t>Development / Economics / Governance / Agriculture</t>
+        </is>
+      </c>
+      <c r="O92" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P92" s="64" t="inlineStr">
+        <is>
+          <t>For mid-career Africans; Kenya eligible; sponsored by Japanese government through AfDB; apply via AfDB Kenya Country Office</t>
+        </is>
+      </c>
+      <c r="Q92" s="64" t="inlineStr">
+        <is>
+          <t>https://www.afdb.org/en/news-and-events/japanese-scholarship-program</t>
+        </is>
+      </c>
+      <c r="R92" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="64" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="64" t="inlineStr">
+        <is>
+          <t>Rotary Peace Fellowship</t>
+        </is>
+      </c>
+      <c r="C93" s="64" t="inlineStr">
+        <is>
+          <t>Masters in peace and conflict studies or professional development certificate</t>
+        </is>
+      </c>
+      <c r="D93" s="64" t="inlineStr">
+        <is>
+          <t>Rotary Peace Centres (Duke/UNC, Uppsala, ICU Japan, Bradford, Chulalongkorn, EARTH)</t>
+        </is>
+      </c>
+      <c r="E93" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F93" s="64" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="G93" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 95 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H93" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + stipend + travel + internship costs</t>
+        </is>
+      </c>
+      <c r="I93" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J93" s="64" t="inlineStr">
+        <is>
+          <t>High English proficiency</t>
+        </is>
+      </c>
+      <c r="K93" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L93" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="64" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="N93" s="64" t="inlineStr">
+        <is>
+          <t>Peace / Conflict Resolution / Development</t>
+        </is>
+      </c>
+      <c r="O93" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P93" s="64" t="inlineStr">
+        <is>
+          <t>For peace practitioners with 3+ years relevant experience; Kenya eligible; apply via Rotary club or directly</t>
+        </is>
+      </c>
+      <c r="Q93" s="64" t="inlineStr">
+        <is>
+          <t>https://www.rotary.org/en/our-programs/peace-fellowships</t>
+        </is>
+      </c>
+      <c r="R93" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="64" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="64" t="inlineStr">
+        <is>
+          <t>ILO / ITC-ILO Masters (Turin)</t>
+        </is>
+      </c>
+      <c r="C94" s="64" t="inlineStr">
+        <is>
+          <t>Masters in labour, human rights, development management</t>
+        </is>
+      </c>
+      <c r="D94" s="64" t="inlineStr">
+        <is>
+          <t>International Training Centre of the ILO, Turin</t>
+        </is>
+      </c>
+      <c r="E94" s="64" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="F94" s="64" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+      <c r="G94" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 201 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H94" s="64" t="inlineStr">
+        <is>
+          <t>Partial: fees subsidised; some full scholarships via donor countries</t>
+        </is>
+      </c>
+      <c r="I94" s="64" t="inlineStr">
+        <is>
+          <t>Partial (unless scholarship awarded)</t>
+        </is>
+      </c>
+      <c r="J94" s="64" t="inlineStr">
+        <is>
+          <t>English or French</t>
+        </is>
+      </c>
+      <c r="K94" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L94" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N94" s="64" t="inlineStr">
+        <is>
+          <t>Labour Rights / Development / HR Management</t>
+        </is>
+      </c>
+      <c r="O94" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P94" s="64" t="inlineStr">
+        <is>
+          <t>Fully funded places available for candidates from developing countries via bilateral agreements; Turin campus</t>
+        </is>
+      </c>
+      <c r="Q94" s="64" t="inlineStr">
+        <is>
+          <t>https://www.itcilo.org/en/masters</t>
+        </is>
+      </c>
+      <c r="R94" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="64" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="64" t="inlineStr">
+        <is>
+          <t>Indian Government Scholarship (ICCR)</t>
+        </is>
+      </c>
+      <c r="C95" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at Indian universities (all fields)</t>
+        </is>
+      </c>
+      <c r="D95" s="64" t="inlineStr">
+        <is>
+          <t>IITs, IIMs, JNU, Delhi University, and other leading institutions</t>
+        </is>
+      </c>
+      <c r="E95" s="64" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F95" s="64" t="inlineStr">
+        <is>
+          <t>2027-03-31</t>
+        </is>
+      </c>
+      <c r="G95" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 231 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H95" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + monthly stipend + accommodation + flights</t>
+        </is>
+      </c>
+      <c r="I95" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J95" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K95" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L95" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N95" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O95" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P95" s="64" t="inlineStr">
+        <is>
+          <t>Apply via High Commission of India in Nairobi; wide field coverage; several hundred places per year for Africa</t>
+        </is>
+      </c>
+      <c r="Q95" s="64" t="inlineStr">
+        <is>
+          <t>https://www.iccr.gov.in/scholarships</t>
+        </is>
+      </c>
+      <c r="R95" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="64" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="64" t="inlineStr">
+        <is>
+          <t>Israeli Government Scholarship (MASHAV)</t>
+        </is>
+      </c>
+      <c r="C96" s="64" t="inlineStr">
+        <is>
+          <t>Masters or certificate courses in agriculture, water, health, development</t>
+        </is>
+      </c>
+      <c r="D96" s="64" t="inlineStr">
+        <is>
+          <t>Hebrew University, Weizmann Institute, Technion, and others</t>
+        </is>
+      </c>
+      <c r="E96" s="64" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="F96" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G96" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H96" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + accommodation + stipend + flights</t>
+        </is>
+      </c>
+      <c r="I96" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J96" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K96" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L96" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N96" s="64" t="inlineStr">
+        <is>
+          <t>Agriculture / Water / Development / Health</t>
+        </is>
+      </c>
+      <c r="O96" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P96" s="64" t="inlineStr">
+        <is>
+          <t>Apply via Israeli Embassy in Nairobi; Kenya has bilateral relations; strong water and agriculture programmes</t>
+        </is>
+      </c>
+      <c r="Q96" s="64" t="inlineStr">
+        <is>
+          <t>https://mashav.mfa.gov.il</t>
+        </is>
+      </c>
+      <c r="R96" s="65" t="inlineStr">
+        <is>
+          <t>Global - Agriculture</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="64" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="64" t="inlineStr">
+        <is>
+          <t>Taiwanese Government Scholarship (MOFA Taiwan Scholarship)</t>
+        </is>
+      </c>
+      <c r="C97" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at Taiwanese universities (all fields)</t>
+        </is>
+      </c>
+      <c r="D97" s="64" t="inlineStr">
+        <is>
+          <t>NTU, NTHU, NCKU, and many others</t>
+        </is>
+      </c>
+      <c r="E97" s="64" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="F97" s="64" t="inlineStr">
+        <is>
+          <t>2027-03-31</t>
+        </is>
+      </c>
+      <c r="G97" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 231 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H97" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + monthly stipend TWD 15,000-20,000 + health insurance</t>
+        </is>
+      </c>
+      <c r="I97" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J97" s="64" t="inlineStr">
+        <is>
+          <t>English or Mandarin</t>
+        </is>
+      </c>
+      <c r="K97" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L97" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N97" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O97" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P97" s="64" t="inlineStr">
+        <is>
+          <t>Apply via MOFA or Taiwanese representative office; excellent engineering and sciences programmes; growing Kenya-Taiwan engagement</t>
+        </is>
+      </c>
+      <c r="Q97" s="64" t="inlineStr">
+        <is>
+          <t>https://www.roc-taiwan.org/scholarships</t>
+        </is>
+      </c>
+      <c r="R97" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="64" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="64" t="inlineStr">
+        <is>
+          <t>South Korean KOICA Fellowship Program</t>
+        </is>
+      </c>
+      <c r="C98" s="64" t="inlineStr">
+        <is>
+          <t>Masters at Korean universities (development-related fields)</t>
+        </is>
+      </c>
+      <c r="D98" s="64" t="inlineStr">
+        <is>
+          <t>Various Korean universities</t>
+        </is>
+      </c>
+      <c r="E98" s="64" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="F98" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G98" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H98" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + accommodation + stipend + flights</t>
+        </is>
+      </c>
+      <c r="I98" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J98" s="64" t="inlineStr">
+        <is>
+          <t>English (Korean language course included)</t>
+        </is>
+      </c>
+      <c r="K98" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L98" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N98" s="64" t="inlineStr">
+        <is>
+          <t>Development / Agriculture / ICT / Governance</t>
+        </is>
+      </c>
+      <c r="O98" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P98" s="64" t="inlineStr">
+        <is>
+          <t>Separate from GKS; administered by KOICA development agency; apply via KOICA Kenya office</t>
+        </is>
+      </c>
+      <c r="Q98" s="64" t="inlineStr">
+        <is>
+          <t>https://www.koica.go.kr</t>
+        </is>
+      </c>
+      <c r="R98" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="64" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="64" t="inlineStr">
+        <is>
+          <t>Brazilian Government Scholarship (CAPES-PrInt / CNPq)</t>
+        </is>
+      </c>
+      <c r="C99" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at Brazilian universities</t>
+        </is>
+      </c>
+      <c r="D99" s="64" t="inlineStr">
+        <is>
+          <t>USP, UNICAMP, UNESP, Embrapa and others</t>
+        </is>
+      </c>
+      <c r="E99" s="64" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F99" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G99" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H99" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + monthly stipend + health insurance + flights</t>
+        </is>
+      </c>
+      <c r="I99" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J99" s="64" t="inlineStr">
+        <is>
+          <t>Portuguese (language course may be included) or English for some programmes</t>
+        </is>
+      </c>
+      <c r="K99" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L99" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N99" s="64" t="inlineStr">
+        <is>
+          <t>Sciences / Agriculture / Engineering</t>
+        </is>
+      </c>
+      <c r="O99" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P99" s="64" t="inlineStr">
+        <is>
+          <t>Portuguese language is main barrier; strong in tropical agriculture and bioenergy; relevant to Roy's energy work for global coverage</t>
+        </is>
+      </c>
+      <c r="Q99" s="64" t="inlineStr">
+        <is>
+          <t>https://www.capes.gov.br/bolsas-e-auxilios</t>
+        </is>
+      </c>
+      <c r="R99" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="64" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="64" t="inlineStr">
+        <is>
+          <t>Polish Government Scholarship (NAWA)</t>
+        </is>
+      </c>
+      <c r="C100" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at Polish universities (all fields)</t>
+        </is>
+      </c>
+      <c r="D100" s="64" t="inlineStr">
+        <is>
+          <t>Warsaw University of Technology, AGH, Jagiellonian, and others</t>
+        </is>
+      </c>
+      <c r="E100" s="64" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="F100" s="64" t="inlineStr">
+        <is>
+          <t>2027-04-30</t>
+        </is>
+      </c>
+      <c r="G100" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 261 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H100" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + monthly stipend PLN 1,250 + accommodation + health insurance</t>
+        </is>
+      </c>
+      <c r="I100" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J100" s="64" t="inlineStr">
+        <is>
+          <t>English or Polish (programme dependent)</t>
+        </is>
+      </c>
+      <c r="K100" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L100" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N100" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O100" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P100" s="64" t="inlineStr">
+        <is>
+          <t>Apply via NAWA portal; growing Africa scholarship programme; several English-taught masters available</t>
+        </is>
+      </c>
+      <c r="Q100" s="64" t="inlineStr">
+        <is>
+          <t>https://nawa.gov.pl/en/scholars/incoming-to-poland</t>
+        </is>
+      </c>
+      <c r="R100" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="64" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="64" t="inlineStr">
+        <is>
+          <t>Czech Government Scholarship (Government of the Czech Republic)</t>
+        </is>
+      </c>
+      <c r="C101" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at Czech public universities</t>
+        </is>
+      </c>
+      <c r="D101" s="64" t="inlineStr">
+        <is>
+          <t>Czech Technical University, Charles University, Brno University of Technology, and others</t>
+        </is>
+      </c>
+      <c r="E101" s="64" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="F101" s="64" t="inlineStr">
+        <is>
+          <t>2027-03-31</t>
+        </is>
+      </c>
+      <c r="G101" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 231 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H101" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + monthly stipend CZK 7,000-9,000 + accommodation</t>
+        </is>
+      </c>
+      <c r="I101" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J101" s="64" t="inlineStr">
+        <is>
+          <t>Czech (language course provided) or English for selected programmes</t>
+        </is>
+      </c>
+      <c r="K101" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L101" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N101" s="64" t="inlineStr">
+        <is>
+          <t>Engineering / Sciences / Humanities</t>
+        </is>
+      </c>
+      <c r="O101" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P101" s="64" t="inlineStr">
+        <is>
+          <t>Apply via Czech Embassy in Nairobi; Czech language required for many programmes; some English-taught engineering tracks available</t>
+        </is>
+      </c>
+      <c r="Q101" s="64" t="inlineStr">
+        <is>
+          <t>https://www.dzs.cz/en/scholarships/</t>
+        </is>
+      </c>
+      <c r="R101" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="64" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="64" t="inlineStr">
+        <is>
+          <t>Romanian Government Scholarship (Ministry of Education)</t>
+        </is>
+      </c>
+      <c r="C102" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at Romanian public universities</t>
+        </is>
+      </c>
+      <c r="D102" s="64" t="inlineStr">
+        <is>
+          <t>University of Bucharest, Polytechnic University, and others</t>
+        </is>
+      </c>
+      <c r="E102" s="64" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="F102" s="64" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G102" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 49 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H102" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + monthly stipend + accommodation</t>
+        </is>
+      </c>
+      <c r="I102" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J102" s="64" t="inlineStr">
+        <is>
+          <t>Romanian (language course included in first year) or English</t>
+        </is>
+      </c>
+      <c r="K102" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L102" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="64" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="N102" s="64" t="inlineStr">
+        <is>
+          <t>Engineering / Medicine / Sciences</t>
+        </is>
+      </c>
+      <c r="O102" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P102" s="64" t="inlineStr">
+        <is>
+          <t>Apply via Romanian Embassy in Nairobi; strong medicine and engineering; mostly Romanian language taught</t>
+        </is>
+      </c>
+      <c r="Q102" s="64" t="inlineStr">
+        <is>
+          <t>https://www.robursa.gov.ro</t>
+        </is>
+      </c>
+      <c r="R102" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="64" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="64" t="inlineStr">
+        <is>
+          <t>Hungarian Government Scholarship (bilateral Kenya agreement)</t>
+        </is>
+      </c>
+      <c r="C103" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at Hungarian universities</t>
+        </is>
+      </c>
+      <c r="D103" s="64" t="inlineStr">
+        <is>
+          <t>Budapest University of Technology, Semmelweis, and others</t>
+        </is>
+      </c>
+      <c r="E103" s="64" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="F103" s="64" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G103" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 80 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H103" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + monthly stipend + accommodation</t>
+        </is>
+      </c>
+      <c r="I103" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J103" s="64" t="inlineStr">
+        <is>
+          <t>English or Hungarian</t>
+        </is>
+      </c>
+      <c r="K103" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L103" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N103" s="64" t="inlineStr">
+        <is>
+          <t>Engineering / Sciences / Medicine</t>
+        </is>
+      </c>
+      <c r="O103" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P103" s="64" t="inlineStr">
+        <is>
+          <t>Separate from Stipendium Hungaricum; Kenya has bilateral agreement; apply via Hungarian Embassy in Nairobi</t>
+        </is>
+      </c>
+      <c r="Q103" s="64" t="inlineStr">
+        <is>
+          <t>https://tka.hu/international-programmes/scholarship-programmes/bilateral-scholarships</t>
+        </is>
+      </c>
+      <c r="R103" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="64" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="64" t="inlineStr">
+        <is>
+          <t>Moroccan Government Scholarship (AMCI)</t>
+        </is>
+      </c>
+      <c r="C104" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at Moroccan universities</t>
+        </is>
+      </c>
+      <c r="D104" s="64" t="inlineStr">
+        <is>
+          <t>Mohammed V University, Hassan II, UM6P, ENSA and others</t>
+        </is>
+      </c>
+      <c r="E104" s="64" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="F104" s="64" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G104" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 80 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H104" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + monthly allowance MAD 1,500 + accommodation</t>
+        </is>
+      </c>
+      <c r="I104" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J104" s="64" t="inlineStr">
+        <is>
+          <t>Arabic / French / English (programme dependent)</t>
+        </is>
+      </c>
+      <c r="K104" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L104" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N104" s="64" t="inlineStr">
+        <is>
+          <t>Engineering / Agriculture / Sciences / Medicine</t>
+        </is>
+      </c>
+      <c r="O104" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P104" s="64" t="inlineStr">
+        <is>
+          <t>Available to all African countries including Kenya; apply via Moroccan Embassy in Nairobi; strong agriculture and engineering</t>
+        </is>
+      </c>
+      <c r="Q104" s="64" t="inlineStr">
+        <is>
+          <t>https://www.amci.ma</t>
+        </is>
+      </c>
+      <c r="R104" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="64" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="64" t="inlineStr">
+        <is>
+          <t>South African Government Scholarship (DHET)</t>
+        </is>
+      </c>
+      <c r="C105" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at South African universities</t>
+        </is>
+      </c>
+      <c r="D105" s="64" t="inlineStr">
+        <is>
+          <t>UCT, Stellenbosch, Wits, UP, and others</t>
+        </is>
+      </c>
+      <c r="E105" s="64" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F105" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G105" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H105" s="64" t="inlineStr">
+        <is>
+          <t>Partial: tuition support + stipend</t>
+        </is>
+      </c>
+      <c r="I105" s="64" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J105" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K105" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L105" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N105" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O105" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P105" s="64" t="inlineStr">
+        <is>
+          <t>Regional African scholarship; Kenya eligible; apply via DHET or directly to SA universities; strong engineering and business schools</t>
+        </is>
+      </c>
+      <c r="Q105" s="64" t="inlineStr">
+        <is>
+          <t>https://www.dhet.gov.za</t>
+        </is>
+      </c>
+      <c r="R105" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="64" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="64" t="inlineStr">
+        <is>
+          <t>Mwalimu Nyerere African Union Scholarship Scheme</t>
+        </is>
+      </c>
+      <c r="C106" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at AU-designated universities in Africa</t>
+        </is>
+      </c>
+      <c r="D106" s="64" t="inlineStr">
+        <is>
+          <t>Selected AU universities (varies by year)</t>
+        </is>
+      </c>
+      <c r="E106" s="64" t="inlineStr">
+        <is>
+          <t>Africa (multiple)</t>
+        </is>
+      </c>
+      <c r="F106" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G106" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H106" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + monthly stipend + travel within Africa</t>
+        </is>
+      </c>
+      <c r="I106" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J106" s="64" t="inlineStr">
+        <is>
+          <t>English or French</t>
+        </is>
+      </c>
+      <c r="K106" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L106" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N106" s="64" t="inlineStr">
+        <is>
+          <t>All fields (development and African integration focus)</t>
+        </is>
+      </c>
+      <c r="O106" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P106" s="64" t="inlineStr">
+        <is>
+          <t>For African nationals to study within Africa; Kenya eligible; reinforces African talent retention; check AU website for open cycles</t>
+        </is>
+      </c>
+      <c r="Q106" s="64" t="inlineStr">
+        <is>
+          <t>https://au.int/en/education</t>
+        </is>
+      </c>
+      <c r="R106" s="65" t="inlineStr">
+        <is>
+          <t>Global - Social Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="64" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="64" t="inlineStr">
+        <is>
+          <t>PASET Regional Scholarship and Innovation Fund (RSIF)</t>
+        </is>
+      </c>
+      <c r="C107" s="64" t="inlineStr">
+        <is>
+          <t>PhD in ICT, food security, energy, climate change</t>
+        </is>
+      </c>
+      <c r="D107" s="64" t="inlineStr">
+        <is>
+          <t>Various African universities + international partners</t>
+        </is>
+      </c>
+      <c r="E107" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F107" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G107" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H107" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + stipend + research grant</t>
+        </is>
+      </c>
+      <c r="I107" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J107" s="64" t="inlineStr">
+        <is>
+          <t>English or French</t>
+        </is>
+      </c>
+      <c r="K107" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L107" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="64" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="N107" s="64" t="inlineStr">
+        <is>
+          <t>ICT / Energy / Food Security / Climate</t>
+        </is>
+      </c>
+      <c r="O107" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P107" s="64" t="inlineStr">
+        <is>
+          <t>World Bank-supported; East Africa focus; Kenya eligible; check RSIF portal for open calls</t>
+        </is>
+      </c>
+      <c r="Q107" s="64" t="inlineStr">
+        <is>
+          <t>https://paset.org/rsif</t>
+        </is>
+      </c>
+      <c r="R107" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="64" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="64" t="inlineStr">
+        <is>
+          <t>African Capacity Building Foundation (ACBF) Scholarship</t>
+        </is>
+      </c>
+      <c r="C108" s="64" t="inlineStr">
+        <is>
+          <t>Masters in economics, public policy, public administration</t>
+        </is>
+      </c>
+      <c r="D108" s="64" t="inlineStr">
+        <is>
+          <t>African universities</t>
+        </is>
+      </c>
+      <c r="E108" s="64" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="F108" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G108" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H108" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + stipend + research allowance</t>
+        </is>
+      </c>
+      <c r="I108" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J108" s="64" t="inlineStr">
+        <is>
+          <t>English or French</t>
+        </is>
+      </c>
+      <c r="K108" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L108" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N108" s="64" t="inlineStr">
+        <is>
+          <t>Economics / Public Policy / Administration</t>
+        </is>
+      </c>
+      <c r="O108" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P108" s="64" t="inlineStr">
+        <is>
+          <t>For African nationals committed to staying in Africa post-study; Kenya eligible; check ACBF website for current calls</t>
+        </is>
+      </c>
+      <c r="Q108" s="64" t="inlineStr">
+        <is>
+          <t>https://www.acbf-pact.org</t>
+        </is>
+      </c>
+      <c r="R108" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="64" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="64" t="inlineStr">
+        <is>
+          <t>African Institute for Mathematical Sciences (AIMS) Masters</t>
+        </is>
+      </c>
+      <c r="C109" s="64" t="inlineStr">
+        <is>
+          <t>MSc Mathematical Sciences</t>
+        </is>
+      </c>
+      <c r="D109" s="64" t="inlineStr">
+        <is>
+          <t>AIMS centres (Cameroon, Ghana, Rwanda, Senegal, South Africa, Tanzania)</t>
+        </is>
+      </c>
+      <c r="E109" s="64" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="F109" s="64" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="G109" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 156 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H109" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + accommodation + stipend + travel within Africa</t>
+        </is>
+      </c>
+      <c r="I109" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J109" s="64" t="inlineStr">
+        <is>
+          <t>English or French</t>
+        </is>
+      </c>
+      <c r="K109" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L109" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="64" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="N109" s="64" t="inlineStr">
+        <is>
+          <t>Mathematical Sciences / Statistics / Machine Learning</t>
+        </is>
+      </c>
+      <c r="O109" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P109" s="64" t="inlineStr">
+        <is>
+          <t>Intensive 1-year masters; strong alumni network; AIMS South Africa does excellent machine learning programme</t>
+        </is>
+      </c>
+      <c r="Q109" s="64" t="inlineStr">
+        <is>
+          <t>https://www.nexteinstein.org/students/</t>
+        </is>
+      </c>
+      <c r="R109" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="64" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="64" t="inlineStr">
+        <is>
+          <t>Google PhD Fellowship</t>
+        </is>
+      </c>
+      <c r="C110" s="64" t="inlineStr">
+        <is>
+          <t>PhD research fellowship in computer science and AI</t>
+        </is>
+      </c>
+      <c r="D110" s="64" t="inlineStr">
+        <is>
+          <t>Selected universities worldwide (Google partner institutions)</t>
+        </is>
+      </c>
+      <c r="E110" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F110" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G110" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H110" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + annual stipend USD 9,000-15,000 (varies by country)</t>
+        </is>
+      </c>
+      <c r="I110" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J110" s="64" t="inlineStr">
+        <is>
+          <t>High (PhD standard)</t>
+        </is>
+      </c>
+      <c r="K110" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L110" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="64" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="N110" s="64" t="inlineStr">
+        <is>
+          <t>Computer Science / AI / Machine Learning</t>
+        </is>
+      </c>
+      <c r="O110" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P110" s="64" t="inlineStr">
+        <is>
+          <t>Nominated by university -- cannot apply directly; listed for awareness; Kenya-based university nominations rare but growing</t>
+        </is>
+      </c>
+      <c r="Q110" s="64" t="inlineStr">
+        <is>
+          <t>https://research.google/outreach/phd-fellowship/</t>
+        </is>
+      </c>
+      <c r="R110" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="64" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="64" t="inlineStr">
+        <is>
+          <t>Microsoft Research PhD Fellowship</t>
+        </is>
+      </c>
+      <c r="C111" s="64" t="inlineStr">
+        <is>
+          <t>PhD fellowship in computer science and AI</t>
+        </is>
+      </c>
+      <c r="D111" s="64" t="inlineStr">
+        <is>
+          <t>Selected universities (Microsoft Research partner institutions)</t>
+        </is>
+      </c>
+      <c r="E111" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F111" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G111" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H111" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + annual stipend</t>
+        </is>
+      </c>
+      <c r="I111" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J111" s="64" t="inlineStr">
+        <is>
+          <t>High (PhD standard)</t>
+        </is>
+      </c>
+      <c r="K111" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L111" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="64" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="N111" s="64" t="inlineStr">
+        <is>
+          <t>Computer Science / AI / Systems</t>
+        </is>
+      </c>
+      <c r="O111" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P111" s="64" t="inlineStr">
+        <is>
+          <t>Nomination-based via university; Microsoft Research Africa presence growing; listed for awareness</t>
+        </is>
+      </c>
+      <c r="Q111" s="64" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com/en-us/research/academic-program/phd-fellowship/</t>
+        </is>
+      </c>
+      <c r="R111" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="64" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="64" t="inlineStr">
+        <is>
+          <t>Volkswagen Foundation – Initiative for Africa</t>
+        </is>
+      </c>
+      <c r="C112" s="64" t="inlineStr">
+        <is>
+          <t>Research and PhD funding for African scholars</t>
+        </is>
+      </c>
+      <c r="D112" s="64" t="inlineStr">
+        <is>
+          <t>African and German institutions</t>
+        </is>
+      </c>
+      <c r="E112" s="64" t="inlineStr">
+        <is>
+          <t>Germany / Africa</t>
+        </is>
+      </c>
+      <c r="F112" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G112" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H112" s="64" t="inlineStr">
+        <is>
+          <t>Full or partial research grant (varies by programme)</t>
+        </is>
+      </c>
+      <c r="I112" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J112" s="64" t="inlineStr">
+        <is>
+          <t>English or German</t>
+        </is>
+      </c>
+      <c r="K112" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L112" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N112" s="64" t="inlineStr">
+        <is>
+          <t>Sciences / Humanities / Engineering</t>
+        </is>
+      </c>
+      <c r="O112" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P112" s="64" t="inlineStr">
+        <is>
+          <t>Multiple funding lines for African researchers; Freigeist fellowships available; check for East Africa-relevant calls</t>
+        </is>
+      </c>
+      <c r="Q112" s="64" t="inlineStr">
+        <is>
+          <t>https://www.volkswagenstiftung.de/en/funding</t>
+        </is>
+      </c>
+      <c r="R112" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="64" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="64" t="inlineStr">
+        <is>
+          <t>Sasakawa Young Leaders Fellowship Fund (SYLFF)</t>
+        </is>
+      </c>
+      <c r="C113" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at SYLFF-member universities</t>
+        </is>
+      </c>
+      <c r="D113" s="64" t="inlineStr">
+        <is>
+          <t>Selected SYLFF partner universities worldwide</t>
+        </is>
+      </c>
+      <c r="E113" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F113" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G113" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H113" s="64" t="inlineStr">
+        <is>
+          <t>Partial: fellowship stipend for study period</t>
+        </is>
+      </c>
+      <c r="I113" s="64" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J113" s="64" t="inlineStr">
+        <is>
+          <t>English or language of host institution</t>
+        </is>
+      </c>
+      <c r="K113" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L113" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N113" s="64" t="inlineStr">
+        <is>
+          <t>All fields (leadership and civil society focus)</t>
+        </is>
+      </c>
+      <c r="O113" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P113" s="64" t="inlineStr">
+        <is>
+          <t>Must apply through a SYLFF-affiliated university; check if any Kenyan or East African universities are members</t>
+        </is>
+      </c>
+      <c r="Q113" s="64" t="inlineStr">
+        <is>
+          <t>https://www.sylff.org</t>
+        </is>
+      </c>
+      <c r="R113" s="65" t="inlineStr">
+        <is>
+          <t>Global - Social Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="64" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="64" t="inlineStr">
+        <is>
+          <t>WHO Long-Term Fellowship</t>
+        </is>
+      </c>
+      <c r="C114" s="64" t="inlineStr">
+        <is>
+          <t>Masters-level training in public health fields</t>
+        </is>
+      </c>
+      <c r="D114" s="64" t="inlineStr">
+        <is>
+          <t>WHO-accredited institutions worldwide</t>
+        </is>
+      </c>
+      <c r="E114" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F114" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G114" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H114" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + stipend + travel + health insurance</t>
+        </is>
+      </c>
+      <c r="I114" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J114" s="64" t="inlineStr">
+        <is>
+          <t>English or French</t>
+        </is>
+      </c>
+      <c r="K114" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L114" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N114" s="64" t="inlineStr">
+        <is>
+          <t>Public Health / Medicine / Epidemiology</t>
+        </is>
+      </c>
+      <c r="O114" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P114" s="64" t="inlineStr">
+        <is>
+          <t>Applied for through WHO Kenya Country Office; nomination required from Ministry of Health; competitive</t>
+        </is>
+      </c>
+      <c r="Q114" s="64" t="inlineStr">
+        <is>
+          <t>https://www.who.int/careers/fellowships</t>
+        </is>
+      </c>
+      <c r="R114" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Health</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="64" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="64" t="inlineStr">
+        <is>
+          <t>FAO Fellowships</t>
+        </is>
+      </c>
+      <c r="C115" s="64" t="inlineStr">
+        <is>
+          <t>Masters or certificate training in food security, agriculture, fisheries</t>
+        </is>
+      </c>
+      <c r="D115" s="64" t="inlineStr">
+        <is>
+          <t>FAO partner institutions</t>
+        </is>
+      </c>
+      <c r="E115" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F115" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G115" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H115" s="64" t="inlineStr">
+        <is>
+          <t>Full or partial (varies by programme)</t>
+        </is>
+      </c>
+      <c r="I115" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J115" s="64" t="inlineStr">
+        <is>
+          <t>English or French</t>
+        </is>
+      </c>
+      <c r="K115" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L115" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N115" s="64" t="inlineStr">
+        <is>
+          <t>Agriculture / Food Security / Fisheries</t>
+        </is>
+      </c>
+      <c r="O115" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P115" s="64" t="inlineStr">
+        <is>
+          <t>Applied for through FAO Kenya Country Office; professional experience required</t>
+        </is>
+      </c>
+      <c r="Q115" s="64" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/fellowships</t>
+        </is>
+      </c>
+      <c r="R115" s="65" t="inlineStr">
+        <is>
+          <t>Global - Agriculture</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="64" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="64" t="inlineStr">
+        <is>
+          <t>IAEA Fellowships</t>
+        </is>
+      </c>
+      <c r="C116" s="64" t="inlineStr">
+        <is>
+          <t>Masters-level training in nuclear technology, radiation, food safety, water isotopes</t>
+        </is>
+      </c>
+      <c r="D116" s="64" t="inlineStr">
+        <is>
+          <t>IAEA laboratories and partner institutions (Vienna, Seibersdorf)</t>
+        </is>
+      </c>
+      <c r="E116" s="64" t="inlineStr">
+        <is>
+          <t>Austria / Multiple</t>
+        </is>
+      </c>
+      <c r="F116" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G116" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H116" s="64" t="inlineStr">
+        <is>
+          <t>Full: stipend + accommodation + travel + training materials</t>
+        </is>
+      </c>
+      <c r="I116" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J116" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K116" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L116" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N116" s="64" t="inlineStr">
+        <is>
+          <t>Nuclear Technology / Radiation Safety / Food Irradiation / Water Isotopes</t>
+        </is>
+      </c>
+      <c r="O116" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P116" s="64" t="inlineStr">
+        <is>
+          <t>Applied via Kenya Nuclear Regulatory Authority or government; relevant to water resources and food safety</t>
+        </is>
+      </c>
+      <c r="Q116" s="64" t="inlineStr">
+        <is>
+          <t>https://www.iaea.org/services/fellowships</t>
+        </is>
+      </c>
+      <c r="R116" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="64" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="64" t="inlineStr">
+        <is>
+          <t>ICTP (Abdus Salam International Centre) Postgraduate Diploma / Fellowship</t>
+        </is>
+      </c>
+      <c r="C117" s="64" t="inlineStr">
+        <is>
+          <t>Postgraduate diploma or research fellowship in physics and mathematics</t>
+        </is>
+      </c>
+      <c r="D117" s="64" t="inlineStr">
+        <is>
+          <t>ICTP, Trieste</t>
+        </is>
+      </c>
+      <c r="E117" s="64" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="F117" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G117" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H117" s="64" t="inlineStr">
+        <is>
+          <t>Full: accommodation + stipend + travel</t>
+        </is>
+      </c>
+      <c r="I117" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J117" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K117" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L117" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N117" s="64" t="inlineStr">
+        <is>
+          <t>Physics / Mathematics / Earth Sciences</t>
+        </is>
+      </c>
+      <c r="O117" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P117" s="64" t="inlineStr">
+        <is>
+          <t>Postgraduate diploma is gateway to PhD; strong Africa programme; Kenyan mathematicians and physicists have participated</t>
+        </is>
+      </c>
+      <c r="Q117" s="64" t="inlineStr">
+        <is>
+          <t>https://www.ictp.it/programmes/fellowships</t>
+        </is>
+      </c>
+      <c r="R117" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="64" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="64" t="inlineStr">
+        <is>
+          <t>Erasmus Mundus – Global Studies (GLOCAL)</t>
+        </is>
+      </c>
+      <c r="C118" s="64" t="inlineStr">
+        <is>
+          <t>MA Global Studies</t>
+        </is>
+      </c>
+      <c r="D118" s="64" t="inlineStr">
+        <is>
+          <t>University of Vienna + Leipzig, Wroclaw, Roskilde</t>
+        </is>
+      </c>
+      <c r="E118" s="64" t="inlineStr">
+        <is>
+          <t>Multiple (EU)</t>
+        </is>
+      </c>
+      <c r="F118" s="64" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="G118" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 156 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H118" s="64" t="inlineStr">
+        <is>
+          <t>Full EU scholarship: tuition + EUR 1,400/mo + travel</t>
+        </is>
+      </c>
+      <c r="I118" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J118" s="64" t="inlineStr">
+        <is>
+          <t>English IELTS 6.5+</t>
+        </is>
+      </c>
+      <c r="K118" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L118" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N118" s="64" t="inlineStr">
+        <is>
+          <t>Global Studies / International Relations</t>
+        </is>
+      </c>
+      <c r="O118" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P118" s="64" t="inlineStr">
+        <is>
+          <t>Non-EU nationals eligible for Erasmus Mundus scholarship; apply via GLOCAL consortium</t>
+        </is>
+      </c>
+      <c r="Q118" s="64" t="inlineStr">
+        <is>
+          <t>https://www.emglobalstudy.eu</t>
+        </is>
+      </c>
+      <c r="R118" s="65" t="inlineStr">
+        <is>
+          <t>Global - Social Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="64" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="64" t="inlineStr">
+        <is>
+          <t>Erasmus Mundus – Environmental Sciences (EnvEuro)</t>
+        </is>
+      </c>
+      <c r="C119" s="64" t="inlineStr">
+        <is>
+          <t>MSc Environmental Sciences</t>
+        </is>
+      </c>
+      <c r="D119" s="64" t="inlineStr">
+        <is>
+          <t>Cologne / Bonn / Copenhagen / Poznan</t>
+        </is>
+      </c>
+      <c r="E119" s="64" t="inlineStr">
+        <is>
+          <t>Multiple (EU)</t>
+        </is>
+      </c>
+      <c r="F119" s="64" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="G119" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 156 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H119" s="64" t="inlineStr">
+        <is>
+          <t>Full EU scholarship: tuition + EUR 1,400/mo + travel</t>
+        </is>
+      </c>
+      <c r="I119" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J119" s="64" t="inlineStr">
+        <is>
+          <t>English IELTS 6.5+</t>
+        </is>
+      </c>
+      <c r="K119" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L119" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N119" s="64" t="inlineStr">
+        <is>
+          <t>Environmental Sciences</t>
+        </is>
+      </c>
+      <c r="O119" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P119" s="64" t="inlineStr">
+        <is>
+          <t>Non-EU eligible for EM scholarship; check Erasmus Mundus catalogue for current 2027 intake</t>
+        </is>
+      </c>
+      <c r="Q119" s="64" t="inlineStr">
+        <is>
+          <t>https://www.eacea.ec.europa.eu/scholarships/erasmus-mundus-catalogue_en</t>
+        </is>
+      </c>
+      <c r="R119" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="64" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="64" t="inlineStr">
+        <is>
+          <t>Erasmus Mundus – Public Health (EUPHORIA / EPHEM)</t>
+        </is>
+      </c>
+      <c r="C120" s="64" t="inlineStr">
+        <is>
+          <t>MSc European Public Health</t>
+        </is>
+      </c>
+      <c r="D120" s="64" t="inlineStr">
+        <is>
+          <t>Maastricht + Antwerp + Oslo + Jagiellonian</t>
+        </is>
+      </c>
+      <c r="E120" s="64" t="inlineStr">
+        <is>
+          <t>Multiple (EU)</t>
+        </is>
+      </c>
+      <c r="F120" s="64" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="G120" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 156 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H120" s="64" t="inlineStr">
+        <is>
+          <t>Full EU scholarship: tuition + EUR 1,400/mo + travel</t>
+        </is>
+      </c>
+      <c r="I120" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J120" s="64" t="inlineStr">
+        <is>
+          <t>English IELTS 6.5+</t>
+        </is>
+      </c>
+      <c r="K120" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L120" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N120" s="64" t="inlineStr">
+        <is>
+          <t>Public Health</t>
+        </is>
+      </c>
+      <c r="O120" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P120" s="64" t="inlineStr">
+        <is>
+          <t>Strong international public health consortium; non-EU nationals eligible for EM scholarship</t>
+        </is>
+      </c>
+      <c r="Q120" s="64" t="inlineStr">
+        <is>
+          <t>https://www.eacea.ec.europa.eu/scholarships/erasmus-mundus-catalogue_en</t>
+        </is>
+      </c>
+      <c r="R120" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Health</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="64" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="64" t="inlineStr">
+        <is>
+          <t>Erasmus Mundus – Quantitative Economics (QEM)</t>
+        </is>
+      </c>
+      <c r="C121" s="64" t="inlineStr">
+        <is>
+          <t>MSc Quantitative Economics</t>
+        </is>
+      </c>
+      <c r="D121" s="64" t="inlineStr">
+        <is>
+          <t>Paris 1 + Ca Foscari Venice + Bielefeld + Barcelona</t>
+        </is>
+      </c>
+      <c r="E121" s="64" t="inlineStr">
+        <is>
+          <t>Multiple (EU)</t>
+        </is>
+      </c>
+      <c r="F121" s="64" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="G121" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 156 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H121" s="64" t="inlineStr">
+        <is>
+          <t>Full EU scholarship: tuition + EUR 1,000/mo + travel</t>
+        </is>
+      </c>
+      <c r="I121" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J121" s="64" t="inlineStr">
+        <is>
+          <t>English IELTS 6.5+ + strong mathematics background</t>
+        </is>
+      </c>
+      <c r="K121" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L121" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="64" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="N121" s="64" t="inlineStr">
+        <is>
+          <t>Economics / Quantitative Methods</t>
+        </is>
+      </c>
+      <c r="O121" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P121" s="64" t="inlineStr">
+        <is>
+          <t>Highly mathematical; strong academic background required; prestigious and competitive</t>
+        </is>
+      </c>
+      <c r="Q121" s="64" t="inlineStr">
+        <is>
+          <t>https://www.qem.eu</t>
+        </is>
+      </c>
+      <c r="R121" s="65" t="inlineStr">
+        <is>
+          <t>Global - Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="64" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="64" t="inlineStr">
+        <is>
+          <t>Erasmus Mundus – Law (EMJMD Law)</t>
+        </is>
+      </c>
+      <c r="C122" s="64" t="inlineStr">
+        <is>
+          <t>LLM (various specialisations)</t>
+        </is>
+      </c>
+      <c r="D122" s="64" t="inlineStr">
+        <is>
+          <t>Various EU law faculties</t>
+        </is>
+      </c>
+      <c r="E122" s="64" t="inlineStr">
+        <is>
+          <t>Multiple (EU)</t>
+        </is>
+      </c>
+      <c r="F122" s="64" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="G122" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 156 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H122" s="64" t="inlineStr">
+        <is>
+          <t>Full EU scholarship: tuition + EUR 1,000/mo + travel</t>
+        </is>
+      </c>
+      <c r="I122" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J122" s="64" t="inlineStr">
+        <is>
+          <t>English IELTS 6.5+ / French</t>
+        </is>
+      </c>
+      <c r="K122" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L122" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N122" s="64" t="inlineStr">
+        <is>
+          <t>Law</t>
+        </is>
+      </c>
+      <c r="O122" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P122" s="64" t="inlineStr">
+        <is>
+          <t>Check Erasmus Mundus catalogue for specific LLM programmes with 2027 intakes</t>
+        </is>
+      </c>
+      <c r="Q122" s="64" t="inlineStr">
+        <is>
+          <t>https://www.eacea.ec.europa.eu/scholarships/erasmus-mundus-catalogue_en</t>
+        </is>
+      </c>
+      <c r="R122" s="65" t="inlineStr">
+        <is>
+          <t>Global - Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="64" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="64" t="inlineStr">
+        <is>
+          <t>Erasmus Mundus – Food Science</t>
+        </is>
+      </c>
+      <c r="C123" s="64" t="inlineStr">
+        <is>
+          <t>MSc Food Science and Technology</t>
+        </is>
+      </c>
+      <c r="D123" s="64" t="inlineStr">
+        <is>
+          <t>Various EU universities</t>
+        </is>
+      </c>
+      <c r="E123" s="64" t="inlineStr">
+        <is>
+          <t>Multiple (EU)</t>
+        </is>
+      </c>
+      <c r="F123" s="64" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="G123" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 156 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H123" s="64" t="inlineStr">
+        <is>
+          <t>Full EU scholarship: tuition + EUR 1,400/mo + travel</t>
+        </is>
+      </c>
+      <c r="I123" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J123" s="64" t="inlineStr">
+        <is>
+          <t>English IELTS 6.5+</t>
+        </is>
+      </c>
+      <c r="K123" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L123" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N123" s="64" t="inlineStr">
+        <is>
+          <t>Food Science / Agriculture</t>
+        </is>
+      </c>
+      <c r="O123" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P123" s="64" t="inlineStr">
+        <is>
+          <t>Relevant to food-water-energy nexus; non-EU eligible for EM scholarship</t>
+        </is>
+      </c>
+      <c r="Q123" s="64" t="inlineStr">
+        <is>
+          <t>https://www.eacea.ec.europa.eu/scholarships/erasmus-mundus-catalogue_en</t>
+        </is>
+      </c>
+      <c r="R123" s="65" t="inlineStr">
+        <is>
+          <t>Global - Agriculture</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="64" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="64" t="inlineStr">
+        <is>
+          <t>Erasmus Mundus – Journalism (EMA / MUNDUS JOURNALISM)</t>
+        </is>
+      </c>
+      <c r="C124" s="64" t="inlineStr">
+        <is>
+          <t>MA International Journalism</t>
+        </is>
+      </c>
+      <c r="D124" s="64" t="inlineStr">
+        <is>
+          <t>Various EU universities (Aarhus, Madrid, Brussels, etc.)</t>
+        </is>
+      </c>
+      <c r="E124" s="64" t="inlineStr">
+        <is>
+          <t>Multiple (EU)</t>
+        </is>
+      </c>
+      <c r="F124" s="64" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="G124" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 156 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H124" s="64" t="inlineStr">
+        <is>
+          <t>Full EU scholarship: tuition + EUR 1,000/mo + travel</t>
+        </is>
+      </c>
+      <c r="I124" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J124" s="64" t="inlineStr">
+        <is>
+          <t>English IELTS 6.5+</t>
+        </is>
+      </c>
+      <c r="K124" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L124" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N124" s="64" t="inlineStr">
+        <is>
+          <t>Journalism / Media Studies</t>
+        </is>
+      </c>
+      <c r="O124" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P124" s="64" t="inlineStr">
+        <is>
+          <t>Non-EU nationals eligible; check Erasmus Mundus journalism programmes for 2027 intake</t>
+        </is>
+      </c>
+      <c r="Q124" s="64" t="inlineStr">
+        <is>
+          <t>https://www.eacea.ec.europa.eu/scholarships/erasmus-mundus-catalogue_en</t>
+        </is>
+      </c>
+      <c r="R124" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="64" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="64" t="inlineStr">
+        <is>
+          <t>Erasmus Mundus – Business (MIM – Masters in Management)</t>
+        </is>
+      </c>
+      <c r="C125" s="64" t="inlineStr">
+        <is>
+          <t>MSc Management / Business</t>
+        </is>
+      </c>
+      <c r="D125" s="64" t="inlineStr">
+        <is>
+          <t>Various EU business schools</t>
+        </is>
+      </c>
+      <c r="E125" s="64" t="inlineStr">
+        <is>
+          <t>Multiple (EU)</t>
+        </is>
+      </c>
+      <c r="F125" s="64" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="G125" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 156 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H125" s="64" t="inlineStr">
+        <is>
+          <t>Full EU scholarship: tuition + EUR 1,000/mo + travel</t>
+        </is>
+      </c>
+      <c r="I125" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J125" s="64" t="inlineStr">
+        <is>
+          <t>English IELTS 6.5+ + GMAT/GRE for some</t>
+        </is>
+      </c>
+      <c r="K125" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L125" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N125" s="64" t="inlineStr">
+        <is>
+          <t>Business / Management</t>
+        </is>
+      </c>
+      <c r="O125" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P125" s="64" t="inlineStr">
+        <is>
+          <t>Check Erasmus Mundus catalogue for management programmes with 2027 intakes</t>
+        </is>
+      </c>
+      <c r="Q125" s="64" t="inlineStr">
+        <is>
+          <t>https://www.eacea.ec.europa.eu/scholarships/erasmus-mundus-catalogue_en</t>
+        </is>
+      </c>
+      <c r="R125" s="65" t="inlineStr">
+        <is>
+          <t>Global - Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="64" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="64" t="inlineStr">
+        <is>
+          <t>COSECSA Fellowship</t>
+        </is>
+      </c>
+      <c r="C126" s="64" t="inlineStr">
+        <is>
+          <t>Surgical training fellowship (MCS ECSA)</t>
+        </is>
+      </c>
+      <c r="D126" s="64" t="inlineStr">
+        <is>
+          <t>COSECSA accredited hospitals and universities across East Africa</t>
+        </is>
+      </c>
+      <c r="E126" s="64" t="inlineStr">
+        <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="F126" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G126" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H126" s="64" t="inlineStr">
+        <is>
+          <t>Partial: training support varies by institution and donor</t>
+        </is>
+      </c>
+      <c r="I126" s="64" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J126" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K126" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L126" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N126" s="64" t="inlineStr">
+        <is>
+          <t>Surgery / Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="O126" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P126" s="64" t="inlineStr">
+        <is>
+          <t>East Africa-based surgical training; Kenya eligible; equivalent to professional clinical qualification</t>
+        </is>
+      </c>
+      <c r="Q126" s="64" t="inlineStr">
+        <is>
+          <t>https://www.cosecsa.org</t>
+        </is>
+      </c>
+      <c r="R126" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Health</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="64" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="64" t="inlineStr">
+        <is>
+          <t>African Field Epidemiology Network (AFENET) FELTP</t>
+        </is>
+      </c>
+      <c r="C127" s="64" t="inlineStr">
+        <is>
+          <t>Masters in Field Epidemiology (FELTP)</t>
+        </is>
+      </c>
+      <c r="D127" s="64" t="inlineStr">
+        <is>
+          <t>Makerere University SPH and regional nodes including Kenya</t>
+        </is>
+      </c>
+      <c r="E127" s="64" t="inlineStr">
+        <is>
+          <t>East Africa / Multiple</t>
+        </is>
+      </c>
+      <c r="F127" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G127" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H127" s="64" t="inlineStr">
+        <is>
+          <t>Full (government-sponsored in most countries via MoH)</t>
+        </is>
+      </c>
+      <c r="I127" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J127" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K127" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L127" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N127" s="64" t="inlineStr">
+        <is>
+          <t>Epidemiology / Public Health</t>
+        </is>
+      </c>
+      <c r="O127" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P127" s="64" t="inlineStr">
+        <is>
+          <t>Kenya FELTP runs through KEMRI/Ministry of Health; highly practical outbreak response training; apply via MoH Kenya</t>
+        </is>
+      </c>
+      <c r="Q127" s="64" t="inlineStr">
+        <is>
+          <t>https://www.afenet.net</t>
+        </is>
+      </c>
+      <c r="R127" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Health</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="64" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="64" t="inlineStr">
+        <is>
+          <t>Global Health Corps Fellowship</t>
+        </is>
+      </c>
+      <c r="C128" s="64" t="inlineStr">
+        <is>
+          <t>1-year fellowship (not a degree) in global health organisations</t>
+        </is>
+      </c>
+      <c r="D128" s="64" t="inlineStr">
+        <is>
+          <t>Global health organisations in US and Africa</t>
+        </is>
+      </c>
+      <c r="E128" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F128" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G128" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H128" s="64" t="inlineStr">
+        <is>
+          <t>Full: stipend + housing + health insurance + professional development</t>
+        </is>
+      </c>
+      <c r="I128" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J128" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K128" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L128" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N128" s="64" t="inlineStr">
+        <is>
+          <t>Global Health / Public Health / Development</t>
+        </is>
+      </c>
+      <c r="O128" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P128" s="64" t="inlineStr">
+        <is>
+          <t>Placed at global health NGOs / governments; early-career focus; strong African placement options</t>
+        </is>
+      </c>
+      <c r="Q128" s="64" t="inlineStr">
+        <is>
+          <t>https://ghcorps.org</t>
+        </is>
+      </c>
+      <c r="R128" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Health</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="64" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="64" t="inlineStr">
+        <is>
+          <t>Said Business School – Africa MBA Scholarships (Oxford)</t>
+        </is>
+      </c>
+      <c r="C129" s="64" t="inlineStr">
+        <is>
+          <t>MBA at Said Business School, University of Oxford</t>
+        </is>
+      </c>
+      <c r="D129" s="64" t="inlineStr">
+        <is>
+          <t>University of Oxford</t>
+        </is>
+      </c>
+      <c r="E129" s="64" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F129" s="64" t="inlineStr">
+        <is>
+          <t>2027-01-06</t>
+        </is>
+      </c>
+      <c r="G129" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 147 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H129" s="64" t="inlineStr">
+        <is>
+          <t>Full or partial (multiple streams including Skoll for social enterprise)</t>
+        </is>
+      </c>
+      <c r="I129" s="64" t="inlineStr">
+        <is>
+          <t>None (MBA fees approx GBP 53,000)</t>
+        </is>
+      </c>
+      <c r="J129" s="64" t="inlineStr">
+        <is>
+          <t>High GMAT / GRE + IELTS 7.5+</t>
+        </is>
+      </c>
+      <c r="K129" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L129" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="64" t="inlineStr">
+        <is>
+          <t>Extremely High</t>
+        </is>
+      </c>
+      <c r="N129" s="64" t="inlineStr">
+        <is>
+          <t>Business / Social Enterprise / Finance</t>
+        </is>
+      </c>
+      <c r="O129" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P129" s="64" t="inlineStr">
+        <is>
+          <t>Highly competitive; Skoll Scholarship specifically targets social entrepreneurs from Africa; strong impact story required</t>
+        </is>
+      </c>
+      <c r="Q129" s="64" t="inlineStr">
+        <is>
+          <t>https://www.sbs.ox.ac.uk/programmes/oxford-mba/fees-and-funding/scholarships</t>
+        </is>
+      </c>
+      <c r="R129" s="65" t="inlineStr">
+        <is>
+          <t>Global - Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="64" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="64" t="inlineStr">
+        <is>
+          <t>Africa Leadership University (ALU) Scholarship</t>
+        </is>
+      </c>
+      <c r="C130" s="64" t="inlineStr">
+        <is>
+          <t>Masters in Entrepreneurial Leadership (MEL)</t>
+        </is>
+      </c>
+      <c r="D130" s="64" t="inlineStr">
+        <is>
+          <t>ALU Rwanda</t>
+        </is>
+      </c>
+      <c r="E130" s="64" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="F130" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G130" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H130" s="64" t="inlineStr">
+        <is>
+          <t>Full and partial scholarships available; up to full tuition + stipend</t>
+        </is>
+      </c>
+      <c r="I130" s="64" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="J130" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K130" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L130" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N130" s="64" t="inlineStr">
+        <is>
+          <t>Entrepreneurship / Leadership / Business</t>
+        </is>
+      </c>
+      <c r="O130" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P130" s="64" t="inlineStr">
+        <is>
+          <t>Africa-focused; pan-African campus; practical leadership model; particularly accessible for East African applicants</t>
+        </is>
+      </c>
+      <c r="Q130" s="64" t="inlineStr">
+        <is>
+          <t>https://www.alueducation.com</t>
+        </is>
+      </c>
+      <c r="R130" s="65" t="inlineStr">
+        <is>
+          <t>Global - Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="64" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="64" t="inlineStr">
+        <is>
+          <t>Hubert H. Humphrey Fellowship (Fulbright HHH)</t>
+        </is>
+      </c>
+      <c r="C131" s="64" t="inlineStr">
+        <is>
+          <t>10-month non-degree professional development in public policy, education, public health, etc.</t>
+        </is>
+      </c>
+      <c r="D131" s="64" t="inlineStr">
+        <is>
+          <t>Various US universities</t>
+        </is>
+      </c>
+      <c r="E131" s="64" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F131" s="64" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G131" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 49 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H131" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + stipend + professional activities + travel</t>
+        </is>
+      </c>
+      <c r="I131" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J131" s="64" t="inlineStr">
+        <is>
+          <t>TOEFL 525+ PBT / 70+ iBT</t>
+        </is>
+      </c>
+      <c r="K131" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L131" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N131" s="64" t="inlineStr">
+        <is>
+          <t>Public Policy / Development / Education / Public Health</t>
+        </is>
+      </c>
+      <c r="O131" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P131" s="64" t="inlineStr">
+        <is>
+          <t>Kenya on eligible country list; apply via USEC Nairobi; mid-career professionals preferred</t>
+        </is>
+      </c>
+      <c r="Q131" s="64" t="inlineStr">
+        <is>
+          <t>https://www.humphreyfellowship.org</t>
+        </is>
+      </c>
+      <c r="R131" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="64" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="64" t="inlineStr">
+        <is>
+          <t>Obama Foundation Scholars Program</t>
+        </is>
+      </c>
+      <c r="C132" s="64" t="inlineStr">
+        <is>
+          <t>One-year leadership and development programme (MA-level)</t>
+        </is>
+      </c>
+      <c r="D132" s="64" t="inlineStr">
+        <is>
+          <t>University of Chicago (Harris) or Columbia SIPA</t>
+        </is>
+      </c>
+      <c r="E132" s="64" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F132" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G132" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H132" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + living stipend + travel</t>
+        </is>
+      </c>
+      <c r="I132" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J132" s="64" t="inlineStr">
+        <is>
+          <t>High English proficiency</t>
+        </is>
+      </c>
+      <c r="K132" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L132" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="64" t="inlineStr">
+        <is>
+          <t>Extremely High</t>
+        </is>
+      </c>
+      <c r="N132" s="64" t="inlineStr">
+        <is>
+          <t>Public Policy / Leadership</t>
+        </is>
+      </c>
+      <c r="O132" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P132" s="64" t="inlineStr">
+        <is>
+          <t>Africa-focused leaders under 40; extraordinarily competitive; check for 2027 cycle opening</t>
+        </is>
+      </c>
+      <c r="Q132" s="64" t="inlineStr">
+        <is>
+          <t>https://www.obama.org/scholars/</t>
+        </is>
+      </c>
+      <c r="R132" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="64" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="64" t="inlineStr">
+        <is>
+          <t>East-West Center Graduate Degree Fellowship</t>
+        </is>
+      </c>
+      <c r="C133" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at University of Hawaii at Manoa (Asia-Pacific focus)</t>
+        </is>
+      </c>
+      <c r="D133" s="64" t="inlineStr">
+        <is>
+          <t>University of Hawaii at Manoa</t>
+        </is>
+      </c>
+      <c r="E133" s="64" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F133" s="64" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="G133" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 81 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H133" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + living allowance + health insurance + activities</t>
+        </is>
+      </c>
+      <c r="I133" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J133" s="64" t="inlineStr">
+        <is>
+          <t>TOEFL 600+ PBT / 100+ iBT or IELTS 7.0+</t>
+        </is>
+      </c>
+      <c r="K133" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L133" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N133" s="64" t="inlineStr">
+        <is>
+          <t>Asia-Pacific Studies / Development / Environment</t>
+        </is>
+      </c>
+      <c r="O133" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P133" s="64" t="inlineStr">
+        <is>
+          <t>Primarily for Asia-Pacific region; African applicants considered on limited basis; listed for global coverage</t>
+        </is>
+      </c>
+      <c r="Q133" s="64" t="inlineStr">
+        <is>
+          <t>https://www.eastwestcenter.org/education/ewc-graduate-degree-fellowship</t>
+        </is>
+      </c>
+      <c r="R133" s="65" t="inlineStr">
+        <is>
+          <t>Global - Social Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="64" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="64" t="inlineStr">
+        <is>
+          <t>Swiss Excellence Scholarships (FCS)</t>
+        </is>
+      </c>
+      <c r="C134" s="64" t="inlineStr">
+        <is>
+          <t>PhD or postdoc research at Swiss universities</t>
+        </is>
+      </c>
+      <c r="D134" s="64" t="inlineStr">
+        <is>
+          <t>ETH Zurich, EPFL, Swiss universities</t>
+        </is>
+      </c>
+      <c r="E134" s="64" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="F134" s="64" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="G134" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 95 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H134" s="64" t="inlineStr">
+        <is>
+          <t>Full: monthly stipend + housing + health insurance + travel</t>
+        </is>
+      </c>
+      <c r="I134" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J134" s="64" t="inlineStr">
+        <is>
+          <t>English / French / German</t>
+        </is>
+      </c>
+      <c r="K134" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L134" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N134" s="64" t="inlineStr">
+        <is>
+          <t>All fields (research focus)</t>
+        </is>
+      </c>
+      <c r="O134" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P134" s="64" t="inlineStr">
+        <is>
+          <t>Apply via Swiss Embassy in Nairobi; deadline approx Nov each year; mainly research/PhD level</t>
+        </is>
+      </c>
+      <c r="Q134" s="64" t="inlineStr">
+        <is>
+          <t>https://www.sbfi.admin.ch/sbfi/en/home/education/scholarships-and-grants/swiss-government-excellence-scholarships.html</t>
+        </is>
+      </c>
+      <c r="R134" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="64" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="64" t="inlineStr">
+        <is>
+          <t>Spanish Government Scholarship (MAEC-AECID)</t>
+        </is>
+      </c>
+      <c r="C135" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at Spanish universities</t>
+        </is>
+      </c>
+      <c r="D135" s="64" t="inlineStr">
+        <is>
+          <t>Various Spanish universities</t>
+        </is>
+      </c>
+      <c r="E135" s="64" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F135" s="64" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G135" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 49 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H135" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + monthly stipend + travel + insurance</t>
+        </is>
+      </c>
+      <c r="I135" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J135" s="64" t="inlineStr">
+        <is>
+          <t>Spanish B2+ required</t>
+        </is>
+      </c>
+      <c r="K135" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L135" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N135" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O135" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P135" s="64" t="inlineStr">
+        <is>
+          <t>Kenya eligible; Spanish language is main barrier; AECID also funds short training programmes in Spanish</t>
+        </is>
+      </c>
+      <c r="Q135" s="64" t="inlineStr">
+        <is>
+          <t>https://www.aecid.es/EN/becas-y-lectorados</t>
+        </is>
+      </c>
+      <c r="R135" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="64" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="64" t="inlineStr">
+        <is>
+          <t>Belgian ARES Scholarship</t>
+        </is>
+      </c>
+      <c r="C136" s="64" t="inlineStr">
+        <is>
+          <t>Masters at Belgian universities (development-related fields)</t>
+        </is>
+      </c>
+      <c r="D136" s="64" t="inlineStr">
+        <is>
+          <t>UCLouvain, ULiege, ULB, etc.</t>
+        </is>
+      </c>
+      <c r="E136" s="64" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="F136" s="64" t="inlineStr">
+        <is>
+          <t>2027-02-01</t>
+        </is>
+      </c>
+      <c r="G136" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 173 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H136" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + monthly allowance + travel</t>
+        </is>
+      </c>
+      <c r="I136" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J136" s="64" t="inlineStr">
+        <is>
+          <t>French proficiency required for most programmes</t>
+        </is>
+      </c>
+      <c r="K136" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L136" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N136" s="64" t="inlineStr">
+        <is>
+          <t>Development / Agriculture / Health / Engineering</t>
+        </is>
+      </c>
+      <c r="O136" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P136" s="64" t="inlineStr">
+        <is>
+          <t>Kenya eligible; French language requirement for most programmes; check ARES website for English-taught options</t>
+        </is>
+      </c>
+      <c r="Q136" s="64" t="inlineStr">
+        <is>
+          <t>https://www.ares-ac.be/en/cooperation-au-developpement/scholarships</t>
+        </is>
+      </c>
+      <c r="R136" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="64" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="64" t="inlineStr">
+        <is>
+          <t>Austrian Government Scholarship (OeAD)</t>
+        </is>
+      </c>
+      <c r="C137" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at Austrian universities</t>
+        </is>
+      </c>
+      <c r="D137" s="64" t="inlineStr">
+        <is>
+          <t>University of Vienna, TU Wien, etc.</t>
+        </is>
+      </c>
+      <c r="E137" s="64" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="F137" s="64" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+      <c r="G137" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 201 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H137" s="64" t="inlineStr">
+        <is>
+          <t>Monthly stipend approx EUR 1,050 -- tuition varies</t>
+        </is>
+      </c>
+      <c r="I137" s="64" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J137" s="64" t="inlineStr">
+        <is>
+          <t>English / French / German</t>
+        </is>
+      </c>
+      <c r="K137" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L137" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N137" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O137" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P137" s="64" t="inlineStr">
+        <is>
+          <t>Apply online via OeAD portal; Kenya eligible; deadline approx Mar each year</t>
+        </is>
+      </c>
+      <c r="Q137" s="64" t="inlineStr">
+        <is>
+          <t>https://oead.at/en/to-austria/grants-and-scholarships/</t>
+        </is>
+      </c>
+      <c r="R137" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="64" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="64" t="inlineStr">
+        <is>
+          <t>Islamic Development Bank Merit Scholarship (IsDB)</t>
+        </is>
+      </c>
+      <c r="C138" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at IsDB-approved universities</t>
+        </is>
+      </c>
+      <c r="D138" s="64" t="inlineStr">
+        <is>
+          <t>Various universities in IsDB member countries</t>
+        </is>
+      </c>
+      <c r="E138" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F138" s="64" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G138" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 141 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H138" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + monthly stipend + travel + health insurance</t>
+        </is>
+      </c>
+      <c r="I138" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J138" s="64" t="inlineStr">
+        <is>
+          <t>English or Arabic</t>
+        </is>
+      </c>
+      <c r="K138" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L138" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N138" s="64" t="inlineStr">
+        <is>
+          <t>All fields (development focus)</t>
+        </is>
+      </c>
+      <c r="O138" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P138" s="64" t="inlineStr">
+        <is>
+          <t>Kenya is IsDB member country; Muslim applicants or nationals of member countries; check IsDB website for current cycle</t>
+        </is>
+      </c>
+      <c r="Q138" s="64" t="inlineStr">
+        <is>
+          <t>https://www.isdb.org/merit-scholarship-programme</t>
+        </is>
+      </c>
+      <c r="R138" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="64" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="64" t="inlineStr">
+        <is>
+          <t>OPEC Fund for International Development Scholarship</t>
+        </is>
+      </c>
+      <c r="C139" s="64" t="inlineStr">
+        <is>
+          <t>Masters at accredited universities in member countries</t>
+        </is>
+      </c>
+      <c r="D139" s="64" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="E139" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F139" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G139" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H139" s="64" t="inlineStr">
+        <is>
+          <t>Partial: up to USD 10,000/year</t>
+        </is>
+      </c>
+      <c r="I139" s="64" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J139" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K139" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L139" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N139" s="64" t="inlineStr">
+        <is>
+          <t>Development / Energy / Economics</t>
+        </is>
+      </c>
+      <c r="O139" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P139" s="64" t="inlineStr">
+        <is>
+          <t>Kenya eligible as beneficiary country; check OPEC Fund website for open calls</t>
+        </is>
+      </c>
+      <c r="Q139" s="64" t="inlineStr">
+        <is>
+          <t>https://opecfund.org/operations/grants/scholarships</t>
+        </is>
+      </c>
+      <c r="R139" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="64" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="64" t="inlineStr">
+        <is>
+          <t>Carnegie Corporation of New York – African Scholars</t>
+        </is>
+      </c>
+      <c r="C140" s="64" t="inlineStr">
+        <is>
+          <t>PhD funding and research support at African universities</t>
+        </is>
+      </c>
+      <c r="D140" s="64" t="inlineStr">
+        <is>
+          <t>African universities</t>
+        </is>
+      </c>
+      <c r="E140" s="64" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="F140" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G140" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H140" s="64" t="inlineStr">
+        <is>
+          <t>Research grant / fellowship (varies)</t>
+        </is>
+      </c>
+      <c r="I140" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J140" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K140" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L140" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N140" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O140" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P140" s="64" t="inlineStr">
+        <is>
+          <t>Primarily supports African scholars at African institutions; check Carnegie website for current grant cycles</t>
+        </is>
+      </c>
+      <c r="Q140" s="64" t="inlineStr">
+        <is>
+          <t>https://www.carnegie.org/programs/international-program/</t>
+        </is>
+      </c>
+      <c r="R140" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="64" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="64" t="inlineStr">
+        <is>
+          <t>Ford Foundation International Fellowships Program (IFP)</t>
+        </is>
+      </c>
+      <c r="C141" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD in social sciences, humanities, arts</t>
+        </is>
+      </c>
+      <c r="D141" s="64" t="inlineStr">
+        <is>
+          <t>Universities in fellows home regions</t>
+        </is>
+      </c>
+      <c r="E141" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F141" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G141" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H141" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + living + research costs</t>
+        </is>
+      </c>
+      <c r="I141" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J141" s="64" t="inlineStr">
+        <is>
+          <t>Varies by institution</t>
+        </is>
+      </c>
+      <c r="K141" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L141" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N141" s="64" t="inlineStr">
+        <is>
+          <t>Social Sciences / Humanities / Arts</t>
+        </is>
+      </c>
+      <c r="O141" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P141" s="64" t="inlineStr">
+        <is>
+          <t>Focuses on social justice leaders; Kenya eligible; check IFP partner institutions for East Africa</t>
+        </is>
+      </c>
+      <c r="Q141" s="64" t="inlineStr">
+        <is>
+          <t>https://www.fordfoundationfellowships.org</t>
+        </is>
+      </c>
+      <c r="R141" s="65" t="inlineStr">
+        <is>
+          <t>Global - Social Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="64" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="64" t="inlineStr">
+        <is>
+          <t>Open Society Foundations Scholarship Programs</t>
+        </is>
+      </c>
+      <c r="C142" s="64" t="inlineStr">
+        <is>
+          <t>Various masters programmes in social sciences, law, public policy</t>
+        </is>
+      </c>
+      <c r="D142" s="64" t="inlineStr">
+        <is>
+          <t>Various institutions (CEU, OSI partner universities)</t>
+        </is>
+      </c>
+      <c r="E142" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F142" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G142" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H142" s="64" t="inlineStr">
+        <is>
+          <t>Full or substantial funding (varies by programme)</t>
+        </is>
+      </c>
+      <c r="I142" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J142" s="64" t="inlineStr">
+        <is>
+          <t>English proficiency required</t>
+        </is>
+      </c>
+      <c r="K142" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L142" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N142" s="64" t="inlineStr">
+        <is>
+          <t>Social Sciences / Law / Policy</t>
+        </is>
+      </c>
+      <c r="O142" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P142" s="64" t="inlineStr">
+        <is>
+          <t>Multiple streams; check OSF website for East Africa-relevant open calls</t>
+        </is>
+      </c>
+      <c r="Q142" s="64" t="inlineStr">
+        <is>
+          <t>https://www.opensocietyfoundations.org/grants</t>
+        </is>
+      </c>
+      <c r="R142" s="65" t="inlineStr">
+        <is>
+          <t>Global - Social Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="64" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="64" t="inlineStr">
+        <is>
+          <t>Finnish Government Scholarship Pool</t>
+        </is>
+      </c>
+      <c r="C143" s="64" t="inlineStr">
+        <is>
+          <t>PhD-level research visits (3-9 months) at Finnish universities</t>
+        </is>
+      </c>
+      <c r="D143" s="64" t="inlineStr">
+        <is>
+          <t>Finnish universities</t>
+        </is>
+      </c>
+      <c r="E143" s="64" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F143" s="64" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G143" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 49 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H143" s="64" t="inlineStr">
+        <is>
+          <t>Monthly stipend EUR 1,500 for research visit</t>
+        </is>
+      </c>
+      <c r="I143" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J143" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K143" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L143" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N143" s="64" t="inlineStr">
+        <is>
+          <t>All fields (research visit only -- not a taught masters)</t>
+        </is>
+      </c>
+      <c r="O143" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P143" s="64" t="inlineStr">
+        <is>
+          <t>For postgraduate researchers; not a full masters programme; apply via OPH portal</t>
+        </is>
+      </c>
+      <c r="Q143" s="64" t="inlineStr">
+        <is>
+          <t>https://www.oph.fi/en/programmes-and-projects/scholarships-and-grants</t>
+        </is>
+      </c>
+      <c r="R143" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="64" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="64" t="inlineStr">
+        <is>
+          <t>TWAS Research Grants for African Scientists</t>
+        </is>
+      </c>
+      <c r="C144" s="64" t="inlineStr">
+        <is>
+          <t>PhD or postdoc research grant</t>
+        </is>
+      </c>
+      <c r="D144" s="64" t="inlineStr">
+        <is>
+          <t>Home institution in Africa</t>
+        </is>
+      </c>
+      <c r="E144" s="64" t="inlineStr">
+        <is>
+          <t>Kenya / Africa</t>
+        </is>
+      </c>
+      <c r="F144" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G144" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H144" s="64" t="inlineStr">
+        <is>
+          <t>Research grant up to USD 15,000</t>
+        </is>
+      </c>
+      <c r="I144" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J144" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K144" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L144" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N144" s="64" t="inlineStr">
+        <is>
+          <t>Sciences</t>
+        </is>
+      </c>
+      <c r="O144" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P144" s="64" t="inlineStr">
+        <is>
+          <t>For scientists in sub-Saharan Africa; not a taught masters but listed for PhD/research awareness</t>
+        </is>
+      </c>
+      <c r="Q144" s="64" t="inlineStr">
+        <is>
+          <t>https://twas.org/opportunity/twas-research-grants</t>
+        </is>
+      </c>
+      <c r="R144" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="64" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="64" t="inlineStr">
+        <is>
+          <t>TWAS-DFG Cooperation Visits Programme</t>
+        </is>
+      </c>
+      <c r="C145" s="64" t="inlineStr">
+        <is>
+          <t>PhD fellowship / research visit at German institution</t>
+        </is>
+      </c>
+      <c r="D145" s="64" t="inlineStr">
+        <is>
+          <t>German research institutions</t>
+        </is>
+      </c>
+      <c r="E145" s="64" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F145" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G145" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H145" s="64" t="inlineStr">
+        <is>
+          <t>Partial: travel + stipend for research visit</t>
+        </is>
+      </c>
+      <c r="I145" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J145" s="64" t="inlineStr">
+        <is>
+          <t>English / German</t>
+        </is>
+      </c>
+      <c r="K145" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L145" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N145" s="64" t="inlineStr">
+        <is>
+          <t>Sciences / Engineering / Agriculture</t>
+        </is>
+      </c>
+      <c r="O145" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P145" s="64" t="inlineStr">
+        <is>
+          <t>For researchers in developing countries including Kenya; short-term research visits</t>
+        </is>
+      </c>
+      <c r="Q145" s="64" t="inlineStr">
+        <is>
+          <t>https://twas.org/opportunity/twas-dfg-cooperation-visits-programme</t>
+        </is>
+      </c>
+      <c r="R145" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
         </is>
       </c>
     </row>
@@ -15322,87 +20954,87 @@
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="38">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Scholarship</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Programme</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>University</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="45" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="45" t="inlineStr">
         <is>
           <t>Funding</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="45" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="J2" s="44" t="inlineStr">
+      <c r="J2" s="45" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="K2" s="45" t="inlineStr">
         <is>
           <t>Elig.</t>
         </is>
       </c>
-      <c r="L2" s="44" t="inlineStr">
+      <c r="L2" s="45" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="M2" s="44" t="inlineStr">
+      <c r="M2" s="45" t="inlineStr">
         <is>
           <t>Competitiveness</t>
         </is>
       </c>
-      <c r="N2" s="44" t="inlineStr">
+      <c r="N2" s="45" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="O2" s="44" t="inlineStr">
+      <c r="O2" s="45" t="inlineStr">
         <is>
           <t>Roy Eligible?</t>
         </is>
       </c>
-      <c r="P2" s="44" t="inlineStr">
+      <c r="P2" s="45" t="inlineStr">
         <is>
           <t>Notes / Action</t>
         </is>
       </c>
-      <c r="Q2" s="44" t="inlineStr">
+      <c r="Q2" s="45" t="inlineStr">
         <is>
           <t>Official Link</t>
         </is>
@@ -15869,87 +21501,87 @@
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="38">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Scholarship</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Programme</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>University</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="45" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="45" t="inlineStr">
         <is>
           <t>Funding</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="45" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="J2" s="44" t="inlineStr">
+      <c r="J2" s="45" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="K2" s="45" t="inlineStr">
         <is>
           <t>Elig.</t>
         </is>
       </c>
-      <c r="L2" s="44" t="inlineStr">
+      <c r="L2" s="45" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="M2" s="44" t="inlineStr">
+      <c r="M2" s="45" t="inlineStr">
         <is>
           <t>Competitiveness</t>
         </is>
       </c>
-      <c r="N2" s="44" t="inlineStr">
+      <c r="N2" s="45" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="O2" s="44" t="inlineStr">
+      <c r="O2" s="45" t="inlineStr">
         <is>
           <t>Roy Eligible?</t>
         </is>
       </c>
-      <c r="P2" s="44" t="inlineStr">
+      <c r="P2" s="45" t="inlineStr">
         <is>
           <t>Notes / Action</t>
         </is>
       </c>
-      <c r="Q2" s="44" t="inlineStr">
+      <c r="Q2" s="45" t="inlineStr">
         <is>
           <t>Official Link</t>
         </is>
@@ -16997,87 +22629,87 @@
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="38">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Scholarship</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Programme</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>University</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="45" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="45" t="inlineStr">
         <is>
           <t>Funding</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="45" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="J2" s="44" t="inlineStr">
+      <c r="J2" s="45" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="K2" s="45" t="inlineStr">
         <is>
           <t>Elig.</t>
         </is>
       </c>
-      <c r="L2" s="44" t="inlineStr">
+      <c r="L2" s="45" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="M2" s="44" t="inlineStr">
+      <c r="M2" s="45" t="inlineStr">
         <is>
           <t>Competitiveness</t>
         </is>
       </c>
-      <c r="N2" s="44" t="inlineStr">
+      <c r="N2" s="45" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="O2" s="44" t="inlineStr">
+      <c r="O2" s="45" t="inlineStr">
         <is>
           <t>Roy Eligible?</t>
         </is>
       </c>
-      <c r="P2" s="44" t="inlineStr">
+      <c r="P2" s="45" t="inlineStr">
         <is>
           <t>Notes / Action</t>
         </is>
       </c>
-      <c r="Q2" s="44" t="inlineStr">
+      <c r="Q2" s="45" t="inlineStr">
         <is>
           <t>Official Link</t>
         </is>
@@ -18789,87 +24421,87 @@
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="38">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Scholarship</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Programme</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>University</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="45" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="45" t="inlineStr">
         <is>
           <t>Funding</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="45" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="J2" s="44" t="inlineStr">
+      <c r="J2" s="45" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="K2" s="45" t="inlineStr">
         <is>
           <t>Elig.</t>
         </is>
       </c>
-      <c r="L2" s="44" t="inlineStr">
+      <c r="L2" s="45" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="M2" s="44" t="inlineStr">
+      <c r="M2" s="45" t="inlineStr">
         <is>
           <t>Competitiveness</t>
         </is>
       </c>
-      <c r="N2" s="44" t="inlineStr">
+      <c r="N2" s="45" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="O2" s="44" t="inlineStr">
+      <c r="O2" s="45" t="inlineStr">
         <is>
           <t>Roy Eligible?</t>
         </is>
       </c>
-      <c r="P2" s="44" t="inlineStr">
+      <c r="P2" s="45" t="inlineStr">
         <is>
           <t>Notes / Action</t>
         </is>
       </c>
-      <c r="Q2" s="44" t="inlineStr">
+      <c r="Q2" s="45" t="inlineStr">
         <is>
           <t>Official Link</t>
         </is>
@@ -19668,87 +25300,87 @@
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="38">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Scholarship</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Programme</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>University</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="45" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="45" t="inlineStr">
         <is>
           <t>Funding</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="45" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="J2" s="44" t="inlineStr">
+      <c r="J2" s="45" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="K2" s="45" t="inlineStr">
         <is>
           <t>Elig.</t>
         </is>
       </c>
-      <c r="L2" s="44" t="inlineStr">
+      <c r="L2" s="45" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="M2" s="44" t="inlineStr">
+      <c r="M2" s="45" t="inlineStr">
         <is>
           <t>Competitiveness</t>
         </is>
       </c>
-      <c r="N2" s="44" t="inlineStr">
+      <c r="N2" s="45" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="O2" s="44" t="inlineStr">
+      <c r="O2" s="45" t="inlineStr">
         <is>
           <t>Roy Eligible?</t>
         </is>
       </c>
-      <c r="P2" s="44" t="inlineStr">
+      <c r="P2" s="45" t="inlineStr">
         <is>
           <t>Notes / Action</t>
         </is>
       </c>
-      <c r="Q2" s="44" t="inlineStr">
+      <c r="Q2" s="45" t="inlineStr">
         <is>
           <t>Official Link</t>
         </is>
@@ -21294,87 +26926,87 @@
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1" s="38">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>Scholarship</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>Programme</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>University</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="45" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="45" t="inlineStr">
         <is>
           <t>Funding</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="45" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="J2" s="44" t="inlineStr">
+      <c r="J2" s="45" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="K2" s="45" t="inlineStr">
         <is>
           <t>Elig.</t>
         </is>
       </c>
-      <c r="L2" s="44" t="inlineStr">
+      <c r="L2" s="45" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="M2" s="44" t="inlineStr">
+      <c r="M2" s="45" t="inlineStr">
         <is>
           <t>Competitiveness</t>
         </is>
       </c>
-      <c r="N2" s="44" t="inlineStr">
+      <c r="N2" s="45" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="O2" s="44" t="inlineStr">
+      <c r="O2" s="45" t="inlineStr">
         <is>
           <t>Roy Eligible?</t>
         </is>
       </c>
-      <c r="P2" s="44" t="inlineStr">
+      <c r="P2" s="45" t="inlineStr">
         <is>
           <t>Notes / Action</t>
         </is>
       </c>
-      <c r="Q2" s="44" t="inlineStr">
+      <c r="Q2" s="45" t="inlineStr">
         <is>
           <t>Official Link</t>
         </is>

--- a/Roy_Okola_Scholarship_Database_LATEST.xlsx
+++ b/Roy_Okola_Scholarship_Database_LATEST.xlsx
@@ -272,7 +272,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -504,6 +504,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -8204,7 +8207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:R145"/>
+  <dimension ref="A1:R170"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="37" min="1" max="1"/>
@@ -8228,7 +8231,7 @@
     <row r="1" ht="21.75" customHeight="1" s="38">
       <c r="A1" s="39" t="inlineStr">
         <is>
-          <t>ROY OKOLA OTIENO — MASTER DATABASE v3 (Cycle 2 Weekly Sync)  |  12 Aug 2026  |  41 Roy Priority + 102 Global = 143 total records</t>
+          <t>ROY OKOLA OTIENO — MASTER DATABASE v3 (Cycle 3 Weekly Sync)  |  24 Aug 2026  |  49 Roy Priority + 119 Global = 168 total records</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8358,7 @@
       </c>
       <c r="G3" s="48" t="inlineStr">
         <is>
-          <t>OPEN NOW – 55 DAYS REMAINING</t>
+          <t>OPEN NOW - 43 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H3" s="47" t="inlineStr">
@@ -8443,7 +8446,7 @@
       </c>
       <c r="G4" s="48" t="inlineStr">
         <is>
-          <t>OPEN NOW – ~80 DAYS REMAINING</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H4" s="47" t="inlineStr">
@@ -8531,7 +8534,7 @@
       </c>
       <c r="G5" s="48" t="inlineStr">
         <is>
-          <t>OPEN NOW – ~80 DAYS REMAINING</t>
+          <t>OPEN NOW - 68 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H5" s="47" t="inlineStr">
@@ -8619,7 +8622,7 @@
       </c>
       <c r="G6" s="53" t="inlineStr">
         <is>
-          <t>OPEN NOW – CHECK DEADLINE URGENTLY (~34 DAYS)</t>
+          <t>URGENT - 22 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H6" s="47" t="inlineStr">
@@ -8707,7 +8710,7 @@
       </c>
       <c r="G7" s="55" t="inlineStr">
         <is>
-          <t>OPENING SOON – Monitor from Oct 2026</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H7" s="47" t="inlineStr">
@@ -8795,7 +8798,7 @@
       </c>
       <c r="G8" s="55" t="inlineStr">
         <is>
-          <t>OPENING SOON – Est. opens 8 Sep 2026</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H8" s="47" t="inlineStr">
@@ -8883,7 +8886,7 @@
       </c>
       <c r="G9" s="57" t="inlineStr">
         <is>
-          <t>LIKELY INELIGIBLE DUE TO MBA – CONFIRM BEFORE APPLYING</t>
+          <t>OPEN NOW - 184 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H9" s="47" t="inlineStr">
@@ -8971,7 +8974,7 @@
       </c>
       <c r="G10" s="55" t="inlineStr">
         <is>
-          <t>OPENING SOON – Est. opens Oct/Nov 2026</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H10" s="47" t="inlineStr">
@@ -9059,7 +9062,7 @@
       </c>
       <c r="G11" s="55" t="inlineStr">
         <is>
-          <t>OPENING SOON – Embassy announcement expected Sep 2026</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H11" s="47" t="inlineStr">
@@ -9147,7 +9150,7 @@
       </c>
       <c r="G12" s="55" t="inlineStr">
         <is>
-          <t>UPCOMING – Opens 1 Mar 2027</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H12" s="47" t="inlineStr">
@@ -9235,7 +9238,7 @@
       </c>
       <c r="G13" s="55" t="inlineStr">
         <is>
-          <t>UPCOMING – Est. Jan 2027</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H13" s="47" t="inlineStr">
@@ -9323,7 +9326,7 @@
       </c>
       <c r="G14" s="55" t="inlineStr">
         <is>
-          <t>UPCOMING – Est. opens Feb 2027</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H14" s="47" t="inlineStr">
@@ -9411,7 +9414,7 @@
       </c>
       <c r="G15" s="55" t="inlineStr">
         <is>
-          <t>UPCOMING – Est. Apr-May 2027</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H15" s="47" t="inlineStr">
@@ -9499,7 +9502,7 @@
       </c>
       <c r="G16" s="57" t="inlineStr">
         <is>
-          <t>INELIGIBLE – PLAN AHEAD FOR 2029/2030 INTAKE</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H16" s="47" t="inlineStr">
@@ -9587,7 +9590,7 @@
       </c>
       <c r="G17" s="62" t="inlineStr">
         <is>
-          <t>Programme application opens 16 Oct 2026</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H17" s="47" t="inlineStr">
@@ -9675,7 +9678,7 @@
       </c>
       <c r="G18" s="55" t="inlineStr">
         <is>
-          <t>UPCOMING – Est. Jan 2027</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H18" s="47" t="inlineStr">
@@ -9763,7 +9766,7 @@
       </c>
       <c r="G19" s="55" t="inlineStr">
         <is>
-          <t>OPENING SOON – Est. Oct-Nov 2026</t>
+          <t>OPEN NOW - 188 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H19" s="47" t="inlineStr">
@@ -9851,7 +9854,7 @@
       </c>
       <c r="G20" s="55" t="inlineStr">
         <is>
-          <t>OPENING SOON – Est. Nov 2026</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H20" s="47" t="inlineStr">
@@ -9939,7 +9942,7 @@
       </c>
       <c r="G21" s="55" t="inlineStr">
         <is>
-          <t>OPENING SOON – Est. Nov 2026</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H21" s="47" t="inlineStr">
@@ -10027,7 +10030,7 @@
       </c>
       <c r="G22" s="55" t="inlineStr">
         <is>
-          <t>OPENING SOON – Est. Oct-Nov 2026</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H22" s="47" t="inlineStr">
@@ -10115,7 +10118,7 @@
       </c>
       <c r="G23" s="63" t="inlineStr">
         <is>
-          <t>NOT YET OPEN – Monitor from Sep 2026</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H23" s="47" t="inlineStr">
@@ -10203,7 +10206,7 @@
       </c>
       <c r="G24" s="63" t="inlineStr">
         <is>
-          <t>NOT YET OPEN – Monitor from Sep 2026</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H24" s="47" t="inlineStr">
@@ -10291,7 +10294,7 @@
       </c>
       <c r="G25" s="63" t="inlineStr">
         <is>
-          <t>NOT YET OPEN – Monitor from Sep 2026</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H25" s="47" t="inlineStr">
@@ -10379,7 +10382,7 @@
       </c>
       <c r="G26" s="62" t="inlineStr">
         <is>
-          <t>VARIES – check each partner</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H26" s="47" t="inlineStr">
@@ -10467,7 +10470,7 @@
       </c>
       <c r="G27" s="62" t="inlineStr">
         <is>
-          <t>Programme application opens 16 Oct 2026</t>
+          <t>OPEN NOW - 144 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H27" s="47" t="inlineStr">
@@ -10555,7 +10558,7 @@
       </c>
       <c r="G28" s="55" t="inlineStr">
         <is>
-          <t>UPCOMING – Est. Jan 2027</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H28" s="47" t="inlineStr">
@@ -10643,7 +10646,7 @@
       </c>
       <c r="G29" s="62" t="inlineStr">
         <is>
-          <t>STATUS UNCLEAR – Programme under restructuring</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H29" s="47" t="inlineStr">
@@ -10731,7 +10734,7 @@
       </c>
       <c r="G30" s="55" t="inlineStr">
         <is>
-          <t>UPCOMING – Check AfDB website</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H30" s="47" t="inlineStr">
@@ -10819,7 +10822,7 @@
       </c>
       <c r="G31" s="55" t="inlineStr">
         <is>
-          <t>UPCOMING – Est. Dec 2026</t>
+          <t>OPEN NOW - 99 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H31" s="47" t="inlineStr">
@@ -10907,7 +10910,7 @@
       </c>
       <c r="G32" s="55" t="inlineStr">
         <is>
-          <t>UPCOMING – Est. Dec 2026</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H32" s="47" t="inlineStr">
@@ -10995,7 +10998,7 @@
       </c>
       <c r="G33" s="55" t="inlineStr">
         <is>
-          <t>OPENING SOON – Est. Nov/Dec 2026</t>
+          <t>OPEN NOW - 122 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H33" s="47" t="inlineStr">
@@ -11083,7 +11086,7 @@
       </c>
       <c r="G34" s="62" t="inlineStr">
         <is>
-          <t>VARIES – check current call</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H34" s="47" t="inlineStr">
@@ -11171,7 +11174,7 @@
       </c>
       <c r="G35" s="55" t="inlineStr">
         <is>
-          <t>UPCOMING – Est. Mar 2027</t>
+          <t>OPEN NOW - 212 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H35" s="47" t="inlineStr">
@@ -11259,7 +11262,7 @@
       </c>
       <c r="G36" s="55" t="inlineStr">
         <is>
-          <t>UPCOMING – Est. Oct 2026</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H36" s="47" t="inlineStr">
@@ -11347,7 +11350,7 @@
       </c>
       <c r="G37" s="62" t="inlineStr">
         <is>
-          <t>VARIES – check ruforum.org for active calls</t>
+          <t>CHECK WEBSITE</t>
         </is>
       </c>
       <c r="H37" s="47" t="inlineStr">
@@ -11435,7 +11438,7 @@
       </c>
       <c r="G38" s="55" t="inlineStr">
         <is>
-          <t>UPCOMING – Est. Feb 2027</t>
+          <t>OPEN NOW - 184 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H38" s="47" t="inlineStr">
@@ -11523,7 +11526,7 @@
       </c>
       <c r="G39" s="57" t="inlineStr">
         <is>
-          <t>CLOSED – Next cycle est. Oct-Nov 2026</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H39" s="47" t="inlineStr">
@@ -11611,7 +11614,7 @@
       </c>
       <c r="G40" s="57" t="inlineStr">
         <is>
-          <t>CLOSED – Next cycle est. Nov 2026</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H40" s="47" t="inlineStr">
@@ -11699,7 +11702,7 @@
       </c>
       <c r="G41" s="57" t="inlineStr">
         <is>
-          <t>CLOSED – AND INELIGIBLE (experience requirement)</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H41" s="47" t="inlineStr">
@@ -11787,7 +11790,7 @@
       </c>
       <c r="G42" s="57" t="inlineStr">
         <is>
-          <t>CLOSED – Next cycle est. Apr-May 2027</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H42" s="47" t="inlineStr">
@@ -11875,7 +11878,7 @@
       </c>
       <c r="G43" s="48" t="inlineStr">
         <is>
-          <t>OPEN NOW – 15 DAYS REMAINING</t>
+          <t>CRITICAL - 3 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H43" s="47" t="inlineStr">
@@ -11963,7 +11966,7 @@
       </c>
       <c r="G44" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 84 DAYS REMAINING</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H44" s="64" t="inlineStr">
@@ -12051,7 +12054,7 @@
       </c>
       <c r="G45" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 62 DAYS REMAINING</t>
+          <t>OPEN NOW - 50 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H45" s="64" t="inlineStr">
@@ -12139,7 +12142,7 @@
       </c>
       <c r="G46" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 93 DAYS REMAINING</t>
+          <t>OPEN NOW - 81 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H46" s="64" t="inlineStr">
@@ -12227,7 +12230,7 @@
       </c>
       <c r="G47" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 187 DAYS REMAINING</t>
+          <t>OPEN NOW - 175 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H47" s="64" t="inlineStr">
@@ -12315,7 +12318,7 @@
       </c>
       <c r="G48" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 93 DAYS REMAINING</t>
+          <t>OPEN NOW - 81 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H48" s="64" t="inlineStr">
@@ -12491,7 +12494,7 @@
       </c>
       <c r="G50" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 156 DAYS REMAINING</t>
+          <t>OPEN NOW - 144 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H50" s="64" t="inlineStr">
@@ -12579,7 +12582,7 @@
       </c>
       <c r="G51" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 84 DAYS REMAINING</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H51" s="64" t="inlineStr">
@@ -12931,7 +12934,7 @@
       </c>
       <c r="G55" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 173 DAYS REMAINING</t>
+          <t>OPEN NOW - 131 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H55" s="64" t="inlineStr">
@@ -13019,7 +13022,7 @@
       </c>
       <c r="G56" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 182 DAYS REMAINING</t>
+          <t>OPEN NOW - 404 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H56" s="64" t="inlineStr">
@@ -13107,7 +13110,7 @@
       </c>
       <c r="G57" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 93 DAYS REMAINING</t>
+          <t>OPEN NOW - 81 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H57" s="64" t="inlineStr">
@@ -13283,7 +13286,7 @@
       </c>
       <c r="G59" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 231 DAYS REMAINING</t>
+          <t>OPEN NOW - 219 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H59" s="64" t="inlineStr">
@@ -13635,7 +13638,7 @@
       </c>
       <c r="G63" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 49 DAYS REMAINING</t>
+          <t>OPEN NOW - 37 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H63" s="64" t="inlineStr">
@@ -13723,7 +13726,7 @@
       </c>
       <c r="G64" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 201 DAYS REMAINING</t>
+          <t>OPEN NOW - 132 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H64" s="64" t="inlineStr">
@@ -13899,7 +13902,7 @@
       </c>
       <c r="G66" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 231 DAYS REMAINING</t>
+          <t>OPEN NOW - 219 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H66" s="64" t="inlineStr">
@@ -13987,7 +13990,7 @@
       </c>
       <c r="G67" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 201 DAYS REMAINING</t>
+          <t>OPEN NOW - 132 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H67" s="64" t="inlineStr">
@@ -14075,7 +14078,7 @@
       </c>
       <c r="G68" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 141 DAYS REMAINING</t>
+          <t>OPEN NOW - 129 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H68" s="64" t="inlineStr">
@@ -14163,7 +14166,7 @@
       </c>
       <c r="G69" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 80 DAYS REMAINING</t>
+          <t>OPEN NOW - 68 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H69" s="64" t="inlineStr">
@@ -14251,7 +14254,7 @@
       </c>
       <c r="G70" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 151 DAYS REMAINING</t>
+          <t>OPEN NOW - 403 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H70" s="64" t="inlineStr">
@@ -14339,7 +14342,7 @@
       </c>
       <c r="G71" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 95 DAYS REMAINING</t>
+          <t>OPEN NOW - 83 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H71" s="64" t="inlineStr">
@@ -14427,7 +14430,7 @@
       </c>
       <c r="G72" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 156 DAYS REMAINING</t>
+          <t>OPEN NOW - 144 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H72" s="64" t="inlineStr">
@@ -14515,7 +14518,7 @@
       </c>
       <c r="G73" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 156 DAYS REMAINING</t>
+          <t>OPEN NOW - 144 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H73" s="64" t="inlineStr">
@@ -14603,7 +14606,7 @@
       </c>
       <c r="G74" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 156 DAYS REMAINING</t>
+          <t>OPEN NOW - 144 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H74" s="64" t="inlineStr">
@@ -14691,7 +14694,7 @@
       </c>
       <c r="G75" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 201 DAYS REMAINING</t>
+          <t>OPEN NOW - 132 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H75" s="64" t="inlineStr">
@@ -14779,7 +14782,7 @@
       </c>
       <c r="G76" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 173 DAYS REMAINING</t>
+          <t>OPEN NOW - 131 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H76" s="64" t="inlineStr">
@@ -14955,7 +14958,7 @@
       </c>
       <c r="G78" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 49 DAYS REMAINING</t>
+          <t>OPEN NOW - 37 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H78" s="64" t="inlineStr">
@@ -15043,7 +15046,7 @@
       </c>
       <c r="G79" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 49 DAYS REMAINING</t>
+          <t>OPEN NOW - 37 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H79" s="64" t="inlineStr">
@@ -16011,7 +16014,7 @@
       </c>
       <c r="G90" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 246 DAYS REMAINING</t>
+          <t>OPEN NOW - 234 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H90" s="64" t="inlineStr">
@@ -16187,7 +16190,7 @@
       </c>
       <c r="G92" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 156 DAYS REMAINING</t>
+          <t>OPEN NOW - 144 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H92" s="64" t="inlineStr">
@@ -16275,7 +16278,7 @@
       </c>
       <c r="G93" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 95 DAYS REMAINING</t>
+          <t>OPEN NOW - 83 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H93" s="64" t="inlineStr">
@@ -16363,7 +16366,7 @@
       </c>
       <c r="G94" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 201 DAYS REMAINING</t>
+          <t>OPEN NOW - 132 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H94" s="64" t="inlineStr">
@@ -16451,7 +16454,7 @@
       </c>
       <c r="G95" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 231 DAYS REMAINING</t>
+          <t>OPEN NOW - 219 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H95" s="64" t="inlineStr">
@@ -16627,7 +16630,7 @@
       </c>
       <c r="G97" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 231 DAYS REMAINING</t>
+          <t>OPEN NOW - 219 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H97" s="64" t="inlineStr">
@@ -16891,7 +16894,7 @@
       </c>
       <c r="G100" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 261 DAYS REMAINING</t>
+          <t>OPEN NOW - 249 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H100" s="64" t="inlineStr">
@@ -16979,7 +16982,7 @@
       </c>
       <c r="G101" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 231 DAYS REMAINING</t>
+          <t>OPEN NOW - 219 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H101" s="64" t="inlineStr">
@@ -17067,7 +17070,7 @@
       </c>
       <c r="G102" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 49 DAYS REMAINING</t>
+          <t>OPEN NOW - 37 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H102" s="64" t="inlineStr">
@@ -17155,7 +17158,7 @@
       </c>
       <c r="G103" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 80 DAYS REMAINING</t>
+          <t>OPEN NOW - 68 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H103" s="64" t="inlineStr">
@@ -17243,7 +17246,7 @@
       </c>
       <c r="G104" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 80 DAYS REMAINING</t>
+          <t>OPEN NOW - 68 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H104" s="64" t="inlineStr">
@@ -17683,7 +17686,7 @@
       </c>
       <c r="G109" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 156 DAYS REMAINING</t>
+          <t>OPEN NOW - 144 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H109" s="64" t="inlineStr">
@@ -18475,7 +18478,7 @@
       </c>
       <c r="G118" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 156 DAYS REMAINING</t>
+          <t>OPEN NOW - 144 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H118" s="64" t="inlineStr">
@@ -18563,7 +18566,7 @@
       </c>
       <c r="G119" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 156 DAYS REMAINING</t>
+          <t>OPEN NOW - 144 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H119" s="64" t="inlineStr">
@@ -18651,7 +18654,7 @@
       </c>
       <c r="G120" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 156 DAYS REMAINING</t>
+          <t>OPEN NOW - 144 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H120" s="64" t="inlineStr">
@@ -18739,7 +18742,7 @@
       </c>
       <c r="G121" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 156 DAYS REMAINING</t>
+          <t>OPEN NOW - 144 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H121" s="64" t="inlineStr">
@@ -18827,7 +18830,7 @@
       </c>
       <c r="G122" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 156 DAYS REMAINING</t>
+          <t>OPEN NOW - 144 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H122" s="64" t="inlineStr">
@@ -18915,7 +18918,7 @@
       </c>
       <c r="G123" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 156 DAYS REMAINING</t>
+          <t>OPEN NOW - 144 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H123" s="64" t="inlineStr">
@@ -19003,7 +19006,7 @@
       </c>
       <c r="G124" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 156 DAYS REMAINING</t>
+          <t>OPEN NOW - 144 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H124" s="64" t="inlineStr">
@@ -19091,7 +19094,7 @@
       </c>
       <c r="G125" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 156 DAYS REMAINING</t>
+          <t>OPEN NOW - 144 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H125" s="64" t="inlineStr">
@@ -19443,7 +19446,7 @@
       </c>
       <c r="G129" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 147 DAYS REMAINING</t>
+          <t>OPEN NOW - 281 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H129" s="64" t="inlineStr">
@@ -19619,7 +19622,7 @@
       </c>
       <c r="G131" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 49 DAYS REMAINING</t>
+          <t>OPEN NOW - 37 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H131" s="64" t="inlineStr">
@@ -19795,7 +19798,7 @@
       </c>
       <c r="G133" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 81 DAYS REMAINING</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H133" s="64" t="inlineStr">
@@ -19883,7 +19886,7 @@
       </c>
       <c r="G134" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 95 DAYS REMAINING</t>
+          <t>OPEN NOW - 83 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H134" s="64" t="inlineStr">
@@ -19971,7 +19974,7 @@
       </c>
       <c r="G135" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 49 DAYS REMAINING</t>
+          <t>OPEN NOW - 37 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H135" s="64" t="inlineStr">
@@ -20059,7 +20062,7 @@
       </c>
       <c r="G136" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 173 DAYS REMAINING</t>
+          <t>OPEN NOW - 131 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H136" s="64" t="inlineStr">
@@ -20147,7 +20150,7 @@
       </c>
       <c r="G137" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 201 DAYS REMAINING</t>
+          <t>OPEN NOW - 132 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H137" s="64" t="inlineStr">
@@ -20235,7 +20238,7 @@
       </c>
       <c r="G138" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 141 DAYS REMAINING</t>
+          <t>OPEN NOW - 129 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H138" s="64" t="inlineStr">
@@ -20675,7 +20678,7 @@
       </c>
       <c r="G143" s="64" t="inlineStr">
         <is>
-          <t>OPEN NOW - 49 DAYS REMAINING</t>
+          <t>OPEN NOW - 37 DAYS REMAINING</t>
         </is>
       </c>
       <c r="H143" s="64" t="inlineStr">
@@ -20903,6 +20906,2206 @@
         </is>
       </c>
       <c r="R145" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="64" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="64" t="inlineStr">
+        <is>
+          <t>Mandela Rhodes Foundation Scholarship</t>
+        </is>
+      </c>
+      <c r="C146" s="64" t="inlineStr">
+        <is>
+          <t>Postgraduate Honours or Masters, any field, at selected South African universities (e.g. MSc Sustainable Energy Engineering - UCT, MEng - Wits, Stellenbosch)</t>
+        </is>
+      </c>
+      <c r="D146" s="64" t="inlineStr">
+        <is>
+          <t>UCT, Wits, Stellenbosch, Rhodes University, and other MRF-recognised SA universities</t>
+        </is>
+      </c>
+      <c r="E146" s="64" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F146" s="64" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G146" s="64" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H146" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + registration + accommodation + meals + personal allowance + medical aid + economy flights</t>
+        </is>
+      </c>
+      <c r="I146" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J146" s="64" t="inlineStr">
+        <is>
+          <t>English (SA university standard)</t>
+        </is>
+      </c>
+      <c r="K146" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L146" s="64" t="n">
+        <v>78</v>
+      </c>
+      <c r="M146" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N146" s="64" t="inlineStr">
+        <is>
+          <t>Leadership / Any field (Roy: Energy/Engineering track available at UCT, Wits)</t>
+        </is>
+      </c>
+      <c r="O146" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="P146" s="64" t="inlineStr">
+        <is>
+          <t>2027 COHORT DEADLINE ALREADY PASSED (14 Apr 2026). Next cycle (2028 intake) opens approx 9 Mar 2027, deadline approx Apr 2027 -- mark calendar now. One of Africa's most prestigious postgraduate scholarships; leadership + academic excellence + citizenship required</t>
+        </is>
+      </c>
+      <c r="Q146" s="64" t="inlineStr">
+        <is>
+          <t>https://www.mandelarhodes.org/scholarship/apply/</t>
+        </is>
+      </c>
+      <c r="R146" s="78" t="inlineStr">
+        <is>
+          <t>Roy Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="64" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="64" t="inlineStr">
+        <is>
+          <t>DAAD Leadership for Africa (LFA) -- East Africa Stream</t>
+        </is>
+      </c>
+      <c r="C147" s="64" t="inlineStr">
+        <is>
+          <t>Masters in any field except Medicine/Veterinary/Dentistry/Law/Fine Arts/Architecture/Nursing (Engineering and Energy Sciences eligible) at German universities</t>
+        </is>
+      </c>
+      <c r="D147" s="64" t="inlineStr">
+        <is>
+          <t>Various German state-recognised universities (applicant selects programme)</t>
+        </is>
+      </c>
+      <c r="E147" s="64" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F147" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G147" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H147" s="64" t="inlineStr">
+        <is>
+          <t>Full: EUR 934/month for 10-24 months + health/accident/liability insurance + German language course</t>
+        </is>
+      </c>
+      <c r="I147" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J147" s="64" t="inlineStr">
+        <is>
+          <t>English or German (language course provided if needed)</t>
+        </is>
+      </c>
+      <c r="K147" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L147" s="64" t="n">
+        <v>74</v>
+      </c>
+      <c r="M147" s="64" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="N147" s="64" t="inlineStr">
+        <is>
+          <t>All fields except excluded list -- Engineering/Energy eligible</t>
+        </is>
+      </c>
+      <c r="O147" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="P147" s="64" t="inlineStr">
+        <is>
+          <t>Explicitly covers Kenya (East Africa stream: Burundi, Kenya, Rwanda, South Sudan, Uganda). Contact lfa.nairobi@daad.de for exact 2027 deadline (funding must begin Oct 2027). Distinct from EPOS -- broader field coverage, no specific development-course restriction</t>
+        </is>
+      </c>
+      <c r="Q147" s="64" t="inlineStr">
+        <is>
+          <t>https://www.daad-kenya.org/en/study-research-in-germany/leadership-for-africa-scholarship/</t>
+        </is>
+      </c>
+      <c r="R147" s="78" t="inlineStr">
+        <is>
+          <t>Roy Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="64" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="64" t="inlineStr">
+        <is>
+          <t>JDS -- Japanese Grant Aid for Human Resource Development Scholarship (Kenya)</t>
+        </is>
+      </c>
+      <c r="C148" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at Japanese universities (English-taught), fields include public policy, engineering, development, governance</t>
+        </is>
+      </c>
+      <c r="D148" s="64" t="inlineStr">
+        <is>
+          <t>Selected Japanese universities via JICA/JDS programme</t>
+        </is>
+      </c>
+      <c r="E148" s="64" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F148" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G148" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H148" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + monthly stipend + accommodation + flights + research support</t>
+        </is>
+      </c>
+      <c r="I148" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J148" s="64" t="inlineStr">
+        <is>
+          <t>English (JDS programmes taught in English)</t>
+        </is>
+      </c>
+      <c r="K148" s="64" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L148" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N148" s="64" t="inlineStr">
+        <is>
+          <t>Public Policy / Governance / Engineering / Development (varies by cycle)</t>
+        </is>
+      </c>
+      <c r="O148" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P148" s="64" t="inlineStr">
+        <is>
+          <t>Primarily targets serving Kenyan government officials nominated by their ministry -- verify current cycle eligibility criteria before treating as open to private-sector applicants. Calls typically open Aug-Oct for following year enrolment. Check jds-scholarship.org/country/kenya</t>
+        </is>
+      </c>
+      <c r="Q148" s="64" t="inlineStr">
+        <is>
+          <t>https://jds-scholarship.org/country/kenya/index.html</t>
+        </is>
+      </c>
+      <c r="R148" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="64" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="64" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Scholars -- University of Cambridge</t>
+        </is>
+      </c>
+      <c r="C149" s="64" t="inlineStr">
+        <is>
+          <t>Masters (any eligible field) at University of Cambridge</t>
+        </is>
+      </c>
+      <c r="D149" s="64" t="inlineStr">
+        <is>
+          <t>University of Cambridge</t>
+        </is>
+      </c>
+      <c r="E149" s="64" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F149" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G149" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H149" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + stipend + travel + mentoring + leadership development</t>
+        </is>
+      </c>
+      <c r="I149" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J149" s="64" t="inlineStr">
+        <is>
+          <t>IELTS/TOEFL (Cambridge standard)</t>
+        </is>
+      </c>
+      <c r="K149" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L149" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="64" t="inlineStr">
+        <is>
+          <t>Extremely High</t>
+        </is>
+      </c>
+      <c r="N149" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O149" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P149" s="64" t="inlineStr">
+        <is>
+          <t>Apply directly to Cambridge Mastercard Foundation Scholars programme; extremely competitive; check Cambridge Trust website for annual deadline</t>
+        </is>
+      </c>
+      <c r="Q149" s="64" t="inlineStr">
+        <is>
+          <t>https://www.mastercardfdn.org/en/what-we-do/our-programs/mastercard-foundation-scholars-program/where-to-apply/</t>
+        </is>
+      </c>
+      <c r="R149" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="64" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="64" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Scholars -- University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="C150" s="64" t="inlineStr">
+        <is>
+          <t>Masters (any eligible field) at University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="D150" s="64" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="E150" s="64" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F150" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G150" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H150" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + stipend + travel + mentoring</t>
+        </is>
+      </c>
+      <c r="I150" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J150" s="64" t="inlineStr">
+        <is>
+          <t>IELTS 6.5+</t>
+        </is>
+      </c>
+      <c r="K150" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L150" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N150" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O150" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P150" s="64" t="inlineStr">
+        <is>
+          <t>Apply directly via University of Edinburgh Mastercard Foundation Scholars page</t>
+        </is>
+      </c>
+      <c r="Q150" s="64" t="inlineStr">
+        <is>
+          <t>https://www.mastercardfdn.org/en/what-we-do/our-programs/mastercard-foundation-scholars-program/where-to-apply/</t>
+        </is>
+      </c>
+      <c r="R150" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="64" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="64" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Scholars -- University of Toronto</t>
+        </is>
+      </c>
+      <c r="C151" s="64" t="inlineStr">
+        <is>
+          <t>Masters (any eligible field) at University of Toronto</t>
+        </is>
+      </c>
+      <c r="D151" s="64" t="inlineStr">
+        <is>
+          <t>University of Toronto</t>
+        </is>
+      </c>
+      <c r="E151" s="64" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F151" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G151" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H151" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + stipend + travel + mentoring</t>
+        </is>
+      </c>
+      <c r="I151" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J151" s="64" t="inlineStr">
+        <is>
+          <t>IELTS 6.5+ / TOEFL 89+</t>
+        </is>
+      </c>
+      <c r="K151" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L151" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N151" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O151" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P151" s="64" t="inlineStr">
+        <is>
+          <t>Apply directly via University of Toronto Mastercard Foundation Scholars page</t>
+        </is>
+      </c>
+      <c r="Q151" s="64" t="inlineStr">
+        <is>
+          <t>https://www.mastercardfdn.org/en/what-we-do/our-programs/mastercard-foundation-scholars-program/where-to-apply/</t>
+        </is>
+      </c>
+      <c r="R151" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="64" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Scholars -- UC Berkeley</t>
+        </is>
+      </c>
+      <c r="C152" s="64" t="inlineStr">
+        <is>
+          <t>Masters (any eligible field) at UC Berkeley</t>
+        </is>
+      </c>
+      <c r="D152" s="64" t="inlineStr">
+        <is>
+          <t>University of California, Berkeley</t>
+        </is>
+      </c>
+      <c r="E152" s="64" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F152" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G152" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H152" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + stipend + travel + mentoring</t>
+        </is>
+      </c>
+      <c r="I152" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J152" s="64" t="inlineStr">
+        <is>
+          <t>IELTS 7.0+ / TOEFL 100+</t>
+        </is>
+      </c>
+      <c r="K152" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L152" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="64" t="inlineStr">
+        <is>
+          <t>Extremely High</t>
+        </is>
+      </c>
+      <c r="N152" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O152" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P152" s="64" t="inlineStr">
+        <is>
+          <t>Apply directly via UC Berkeley Mastercard Foundation Scholars page; highly competitive</t>
+        </is>
+      </c>
+      <c r="Q152" s="64" t="inlineStr">
+        <is>
+          <t>https://www.mastercardfdn.org/en/what-we-do/our-programs/mastercard-foundation-scholars-program/where-to-apply/</t>
+        </is>
+      </c>
+      <c r="R152" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="64" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="64" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Scholars -- McGill University</t>
+        </is>
+      </c>
+      <c r="C153" s="64" t="inlineStr">
+        <is>
+          <t>Masters (any eligible field) at McGill University</t>
+        </is>
+      </c>
+      <c r="D153" s="64" t="inlineStr">
+        <is>
+          <t>McGill University</t>
+        </is>
+      </c>
+      <c r="E153" s="64" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F153" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G153" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H153" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + stipend + travel + mentoring</t>
+        </is>
+      </c>
+      <c r="I153" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J153" s="64" t="inlineStr">
+        <is>
+          <t>IELTS 6.5+</t>
+        </is>
+      </c>
+      <c r="K153" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L153" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N153" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O153" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P153" s="64" t="inlineStr">
+        <is>
+          <t>Apply directly via McGill Mastercard Foundation Scholars page</t>
+        </is>
+      </c>
+      <c r="Q153" s="64" t="inlineStr">
+        <is>
+          <t>https://www.mastercardfdn.org/en/what-we-do/our-programs/mastercard-foundation-scholars-program/where-to-apply/</t>
+        </is>
+      </c>
+      <c r="R153" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="64" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="64" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Scholars -- Makerere University</t>
+        </is>
+      </c>
+      <c r="C154" s="64" t="inlineStr">
+        <is>
+          <t>Masters (any eligible field) at Makerere University</t>
+        </is>
+      </c>
+      <c r="D154" s="64" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="E154" s="64" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="F154" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G154" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H154" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + stipend + accommodation + mentoring</t>
+        </is>
+      </c>
+      <c r="I154" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J154" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K154" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L154" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N154" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O154" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P154" s="64" t="inlineStr">
+        <is>
+          <t>East African regional option -- easier logistics/lower cost of living than Western partners; apply directly via Makerere Mastercard Foundation office</t>
+        </is>
+      </c>
+      <c r="Q154" s="64" t="inlineStr">
+        <is>
+          <t>https://www.mastercardfdn.org/en/what-we-do/our-programs/mastercard-foundation-scholars-program/where-to-apply/</t>
+        </is>
+      </c>
+      <c r="R154" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="64" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="64" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Scholars -- AIMS (African Institute for Mathematical Sciences)</t>
+        </is>
+      </c>
+      <c r="C155" s="64" t="inlineStr">
+        <is>
+          <t>MSc Mathematical Sciences</t>
+        </is>
+      </c>
+      <c r="D155" s="64" t="inlineStr">
+        <is>
+          <t>AIMS centres (Rwanda, Ghana, Senegal, South Africa, Tanzania, Cameroon)</t>
+        </is>
+      </c>
+      <c r="E155" s="64" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="F155" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G155" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H155" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + accommodation + stipend + travel within Africa</t>
+        </is>
+      </c>
+      <c r="I155" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J155" s="64" t="inlineStr">
+        <is>
+          <t>English or French</t>
+        </is>
+      </c>
+      <c r="K155" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L155" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="64" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="N155" s="64" t="inlineStr">
+        <is>
+          <t>Mathematical Sciences / Data Science / Machine Learning</t>
+        </is>
+      </c>
+      <c r="O155" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="P155" s="64" t="inlineStr">
+        <is>
+          <t>Relevant to Roy's energy data analysis background; intensive 1-year programme; strong alumni network in African tech and energy sectors</t>
+        </is>
+      </c>
+      <c r="Q155" s="64" t="inlineStr">
+        <is>
+          <t>https://www.mastercardfdn.org/en/what-we-do/our-programs/mastercard-foundation-scholars-program/where-to-apply/</t>
+        </is>
+      </c>
+      <c r="R155" s="78" t="inlineStr">
+        <is>
+          <t>Roy Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="64" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="64" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Scholars -- University of Pretoria</t>
+        </is>
+      </c>
+      <c r="C156" s="64" t="inlineStr">
+        <is>
+          <t>Masters (any eligible field, strong engineering faculty) at University of Pretoria</t>
+        </is>
+      </c>
+      <c r="D156" s="64" t="inlineStr">
+        <is>
+          <t>University of Pretoria</t>
+        </is>
+      </c>
+      <c r="E156" s="64" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F156" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G156" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H156" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + stipend + accommodation + mentoring</t>
+        </is>
+      </c>
+      <c r="I156" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J156" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K156" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L156" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N156" s="64" t="inlineStr">
+        <is>
+          <t>All fields including Engineering</t>
+        </is>
+      </c>
+      <c r="O156" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="P156" s="64" t="inlineStr">
+        <is>
+          <t>Strong engineering and energy programmes; regional African option; apply via UP Mastercard Foundation office</t>
+        </is>
+      </c>
+      <c r="Q156" s="64" t="inlineStr">
+        <is>
+          <t>https://www.mastercardfdn.org/en/what-we-do/our-programs/mastercard-foundation-scholars-program/where-to-apply/</t>
+        </is>
+      </c>
+      <c r="R156" s="78" t="inlineStr">
+        <is>
+          <t>Roy Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="64" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="64" t="inlineStr">
+        <is>
+          <t>Mastercard Foundation Scholars -- African Leadership University (ALU)</t>
+        </is>
+      </c>
+      <c r="C157" s="64" t="inlineStr">
+        <is>
+          <t>Bachelor's and select Masters programmes, entrepreneurial leadership focus</t>
+        </is>
+      </c>
+      <c r="D157" s="64" t="inlineStr">
+        <is>
+          <t>ALU Rwanda</t>
+        </is>
+      </c>
+      <c r="E157" s="64" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="F157" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G157" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H157" s="64" t="inlineStr">
+        <is>
+          <t>Full and partial scholarships available</t>
+        </is>
+      </c>
+      <c r="I157" s="64" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="J157" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K157" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L157" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N157" s="64" t="inlineStr">
+        <is>
+          <t>Entrepreneurship / Leadership / Business</t>
+        </is>
+      </c>
+      <c r="O157" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P157" s="64" t="inlineStr">
+        <is>
+          <t>Pan-African campus; practical leadership model; check current Masters offerings availability</t>
+        </is>
+      </c>
+      <c r="Q157" s="64" t="inlineStr">
+        <is>
+          <t>https://www.mastercardfdn.org/en/what-we-do/our-programs/mastercard-foundation-scholars-program/where-to-apply/</t>
+        </is>
+      </c>
+      <c r="R157" s="65" t="inlineStr">
+        <is>
+          <t>Global - Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="64" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="64" t="inlineStr">
+        <is>
+          <t>Clarendon Fund Scholarship</t>
+        </is>
+      </c>
+      <c r="C158" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD, any subject at University of Oxford</t>
+        </is>
+      </c>
+      <c r="D158" s="64" t="inlineStr">
+        <is>
+          <t>University of Oxford</t>
+        </is>
+      </c>
+      <c r="E158" s="64" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F158" s="64" t="inlineStr">
+        <is>
+          <t>Dec 2026 - Jan 2027 (course-dependent)</t>
+        </is>
+      </c>
+      <c r="G158" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H158" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + college fees + living stipend</t>
+        </is>
+      </c>
+      <c r="I158" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J158" s="64" t="inlineStr">
+        <is>
+          <t>IELTS 7.0+/TOEFL 100+ (Oxford standard)</t>
+        </is>
+      </c>
+      <c r="K158" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L158" s="64" t="n">
+        <v>76</v>
+      </c>
+      <c r="M158" s="64" t="inlineStr">
+        <is>
+          <t>Extremely High</t>
+        </is>
+      </c>
+      <c r="N158" s="64" t="inlineStr">
+        <is>
+          <t>All fields (Engineering Science, Energy Systems relevant)</t>
+        </is>
+      </c>
+      <c r="O158" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="P158" s="64" t="inlineStr">
+        <is>
+          <t>Oxford's flagship scholarship, all nationalities, all subjects; automatically considered upon applying to an eligible Oxford graduate course; deadline typically follows Oxford's Jan graduate admissions round | LIVE-VERIFIED 2026-08-24: CONFIRMED: no separate application -- automatically considered when applying to an eligible Oxford graduate course by its Dec/Jan funding deadline. Check specific course page for exact date.</t>
+        </is>
+      </c>
+      <c r="Q158" s="64" t="inlineStr">
+        <is>
+          <t>https://www.ox.ac.uk/clarendon</t>
+        </is>
+      </c>
+      <c r="R158" s="78" t="inlineStr">
+        <is>
+          <t>Roy Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="64" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="64" t="inlineStr">
+        <is>
+          <t>Knight-Hennessy Scholars</t>
+        </is>
+      </c>
+      <c r="C159" s="64" t="inlineStr">
+        <is>
+          <t>Any graduate degree (Masters or PhD) at Stanford University</t>
+        </is>
+      </c>
+      <c r="D159" s="64" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+      <c r="E159" s="64" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F159" s="64" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G159" s="64" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H159" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + living stipend + travel for full duration of degree</t>
+        </is>
+      </c>
+      <c r="I159" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J159" s="64" t="inlineStr">
+        <is>
+          <t>TOEFL 100+/IELTS 7.0+ (Stanford standard)</t>
+        </is>
+      </c>
+      <c r="K159" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L159" s="64" t="n">
+        <v>72</v>
+      </c>
+      <c r="M159" s="64" t="inlineStr">
+        <is>
+          <t>Extremely High</t>
+        </is>
+      </c>
+      <c r="N159" s="64" t="inlineStr">
+        <is>
+          <t>All fields (energy, engineering, public policy relevant)</t>
+        </is>
+      </c>
+      <c r="O159" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="P159" s="64" t="inlineStr">
+        <is>
+          <t>Fully funded for entire Stanford graduate programme (up to 3 years); global leadership focus; extremely competitive but explicitly welcomes African applicants | LIVE-VERIFIED 2026-08-24: CONFIRMED: KHS application closes 6 Oct 2026, 1pm Pacific Time. Must also submit separate Stanford graduate degree application by the earlier of the KHS deadline or 1 Dec 2026.</t>
+        </is>
+      </c>
+      <c r="Q159" s="64" t="inlineStr">
+        <is>
+          <t>https://knight-hennessy.stanford.edu</t>
+        </is>
+      </c>
+      <c r="R159" s="78" t="inlineStr">
+        <is>
+          <t>Roy Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="64" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="64" t="inlineStr">
+        <is>
+          <t>Cambridge Trust Scholarship</t>
+        </is>
+      </c>
+      <c r="C160" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD, any subject at University of Cambridge</t>
+        </is>
+      </c>
+      <c r="D160" s="64" t="inlineStr">
+        <is>
+          <t>University of Cambridge</t>
+        </is>
+      </c>
+      <c r="E160" s="64" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F160" s="64" t="inlineStr">
+        <is>
+          <t>Dec 2026 - Jan 2027 (course-dependent)</t>
+        </is>
+      </c>
+      <c r="G160" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H160" s="64" t="inlineStr">
+        <is>
+          <t>Full or partial: tuition + maintenance (varies by award type)</t>
+        </is>
+      </c>
+      <c r="I160" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J160" s="64" t="inlineStr">
+        <is>
+          <t>IELTS 7.5+ (Cambridge standard)</t>
+        </is>
+      </c>
+      <c r="K160" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L160" s="64" t="n">
+        <v>70</v>
+      </c>
+      <c r="M160" s="64" t="inlineStr">
+        <is>
+          <t>Extremely High</t>
+        </is>
+      </c>
+      <c r="N160" s="64" t="inlineStr">
+        <is>
+          <t>All fields including Engineering for Sustainable Development</t>
+        </is>
+      </c>
+      <c r="O160" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="P160" s="64" t="inlineStr">
+        <is>
+          <t>Broader than Gates Cambridge -- includes Cambridge Africa Scholarships and other Trust-funded awards; apply through Cambridge graduate admissions, funding considered automatically | LIVE-VERIFIED 2026-08-24: CONFIRMED: applications for 2027/28 entry open September 2026. Apply through course application in Applicant Portal by course-specific funding deadline (early Dec or early Jan).</t>
+        </is>
+      </c>
+      <c r="Q160" s="64" t="inlineStr">
+        <is>
+          <t>https://www.cambridgetrust.org</t>
+        </is>
+      </c>
+      <c r="R160" s="78" t="inlineStr">
+        <is>
+          <t>Roy Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="64" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="64" t="inlineStr">
+        <is>
+          <t>Commonwealth PhD Scholarship (Split-Site)</t>
+        </is>
+      </c>
+      <c r="C161" s="64" t="inlineStr">
+        <is>
+          <t>PhD, spend time at both home country and UK university, all fields</t>
+        </is>
+      </c>
+      <c r="D161" s="64" t="inlineStr">
+        <is>
+          <t>Various UK universities</t>
+        </is>
+      </c>
+      <c r="E161" s="64" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F161" s="64" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+      <c r="G161" s="64" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+      <c r="H161" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + stipend + flights for UK portion of study</t>
+        </is>
+      </c>
+      <c r="I161" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J161" s="64" t="inlineStr">
+        <is>
+          <t>IELTS 6.5+</t>
+        </is>
+      </c>
+      <c r="K161" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L161" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N161" s="64" t="inlineStr">
+        <is>
+          <t>All fields (development-relevant preferred)</t>
+        </is>
+      </c>
+      <c r="O161" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P161" s="64" t="inlineStr">
+        <is>
+          <t>For PhD candidates already registered at a Kenyan university; funds a period of research at a UK university; Kenya on eligible country list | LIVE-VERIFIED 2026-08-24: CONFIRMED: programme is currently under review and NOT running for the 2026/27 cycle. No 2027 deadline exists. Check cscuk.fcdo.gov.uk periodically for programme reinstatement.</t>
+        </is>
+      </c>
+      <c r="Q161" s="64" t="inlineStr">
+        <is>
+          <t>https://cscuk.fcdo.gov.uk</t>
+        </is>
+      </c>
+      <c r="R161" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="64" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" s="64" t="inlineStr">
+        <is>
+          <t>Commonwealth Rutherford Fellowship</t>
+        </is>
+      </c>
+      <c r="C162" s="64" t="inlineStr">
+        <is>
+          <t>Postdoctoral research fellowship (1-3 years) at UK universities</t>
+        </is>
+      </c>
+      <c r="D162" s="64" t="inlineStr">
+        <is>
+          <t>Various UK universities</t>
+        </is>
+      </c>
+      <c r="E162" s="64" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F162" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G162" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H162" s="64" t="inlineStr">
+        <is>
+          <t>Full: salary + research costs + travel</t>
+        </is>
+      </c>
+      <c r="I162" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J162" s="64" t="inlineStr">
+        <is>
+          <t>IELTS 6.5+</t>
+        </is>
+      </c>
+      <c r="K162" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="L162" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N162" s="64" t="inlineStr">
+        <is>
+          <t>All fields (research focus)</t>
+        </is>
+      </c>
+      <c r="O162" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P162" s="64" t="inlineStr">
+        <is>
+          <t>For early-career researchers who already hold a PhD; not a taught masters; Kenya eligible as Commonwealth member | LIVE-VERIFIED 2026-08-24: No 2027 deadline published yet in search results -- monitor cscuk.fcdo.gov.uk directly.</t>
+        </is>
+      </c>
+      <c r="Q162" s="64" t="inlineStr">
+        <is>
+          <t>https://cscuk.fcdo.gov.uk</t>
+        </is>
+      </c>
+      <c r="R162" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="64" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" s="64" t="inlineStr">
+        <is>
+          <t>Yenching Academy Scholarship</t>
+        </is>
+      </c>
+      <c r="C163" s="64" t="inlineStr">
+        <is>
+          <t>One-year interdisciplinary Master's in China Studies</t>
+        </is>
+      </c>
+      <c r="D163" s="64" t="inlineStr">
+        <is>
+          <t>Peking University</t>
+        </is>
+      </c>
+      <c r="E163" s="64" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F163" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G163" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H163" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + accommodation + stipend + travel + research/language trips</t>
+        </is>
+      </c>
+      <c r="I163" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J163" s="64" t="inlineStr">
+        <is>
+          <t>English (China Studies taught in English)</t>
+        </is>
+      </c>
+      <c r="K163" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L163" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N163" s="64" t="inlineStr">
+        <is>
+          <t>Area Studies / Economics / Public Policy / Politics (China-Africa relations track available)</t>
+        </is>
+      </c>
+      <c r="O163" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P163" s="64" t="inlineStr">
+        <is>
+          <t>Fully funded, global cohort model with strong African representation historically; relevant for those interested in China-Africa energy and development ties | LIVE-VERIFIED 2026-08-24: CONFIRMED: 2027 cohort recruitment information will be released around September 2026. Typical direct-applicant deadline falls Dec-Jan. Monitor yenchingacademy.pku.edu.cn from September.</t>
+        </is>
+      </c>
+      <c r="Q163" s="64" t="inlineStr">
+        <is>
+          <t>https://yenchingacademy.pku.edu.cn</t>
+        </is>
+      </c>
+      <c r="R163" s="65" t="inlineStr">
+        <is>
+          <t>Global - Social Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="64" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" s="64" t="inlineStr">
+        <is>
+          <t>Schwarzman Scholars</t>
+        </is>
+      </c>
+      <c r="C164" s="64" t="inlineStr">
+        <is>
+          <t>One-year Master's in Global Affairs</t>
+        </is>
+      </c>
+      <c r="D164" s="64" t="inlineStr">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+      <c r="E164" s="64" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F164" s="64" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G164" s="64" t="inlineStr">
+        <is>
+          <t>URGENT - 16 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H164" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + room/board + travel + stipend + laptop</t>
+        </is>
+      </c>
+      <c r="I164" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J164" s="64" t="inlineStr">
+        <is>
+          <t>English (Global Affairs taught in English)</t>
+        </is>
+      </c>
+      <c r="K164" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L164" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="64" t="inlineStr">
+        <is>
+          <t>Extremely High</t>
+        </is>
+      </c>
+      <c r="N164" s="64" t="inlineStr">
+        <is>
+          <t>Public Policy / Global Affairs / Economics / Business</t>
+        </is>
+      </c>
+      <c r="O164" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P164" s="64" t="inlineStr">
+        <is>
+          <t>Highly selective global leadership programme; explicitly recruits from Africa; strong alumni network | LIVE-VERIFIED 2026-08-24: CONFIRMED: US/Global application deadline is 9 September 2026, 3pm EDT. Application opened 8 April 2026. Separate earlier deadline exists for China-region applicants (20 May 2026) -- not applicable to Kenya.</t>
+        </is>
+      </c>
+      <c r="Q164" s="64" t="inlineStr">
+        <is>
+          <t>https://www.schwarzmanscholars.org</t>
+        </is>
+      </c>
+      <c r="R164" s="65" t="inlineStr">
+        <is>
+          <t>Global - Public Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="64" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" s="64" t="inlineStr">
+        <is>
+          <t>Weidenfeld-Hoffmann Scholarship and Leadership Programme</t>
+        </is>
+      </c>
+      <c r="C165" s="64" t="inlineStr">
+        <is>
+          <t>Masters at University of Oxford in fields relevant to good governance and economic development</t>
+        </is>
+      </c>
+      <c r="D165" s="64" t="inlineStr">
+        <is>
+          <t>University of Oxford</t>
+        </is>
+      </c>
+      <c r="E165" s="64" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F165" s="64" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="G165" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 342 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H165" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + college fees + living stipend + leadership training</t>
+        </is>
+      </c>
+      <c r="I165" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J165" s="64" t="inlineStr">
+        <is>
+          <t>IELTS 7.0+ (Oxford standard)</t>
+        </is>
+      </c>
+      <c r="K165" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L165" s="64" t="n">
+        <v>68</v>
+      </c>
+      <c r="M165" s="64" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="N165" s="64" t="inlineStr">
+        <is>
+          <t>Public Policy / Economics / Development / Energy Policy</t>
+        </is>
+      </c>
+      <c r="O165" s="64" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="P165" s="64" t="inlineStr">
+        <is>
+          <t>For students from developing/transition countries; leadership development component alongside degree; Kenya eligible | LIVE-VERIFIED 2026-08-24: CONFIRMED: deadline 8 January 2027 (varies slightly by specific graduate course, generally Dec 2026-Jan 2027). Interviews for shortlisted candidates held late April/early May 2027.</t>
+        </is>
+      </c>
+      <c r="Q165" s="64" t="inlineStr">
+        <is>
+          <t>https://www.weidenfeldhoffmann.com</t>
+        </is>
+      </c>
+      <c r="R165" s="78" t="inlineStr">
+        <is>
+          <t>Roy Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="64" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" s="64" t="inlineStr">
+        <is>
+          <t>AAUW International Fellowship</t>
+        </is>
+      </c>
+      <c r="C166" s="64" t="inlineStr">
+        <is>
+          <t>Masters or PhD at accredited US universities (women only)</t>
+        </is>
+      </c>
+      <c r="D166" s="64" t="inlineStr">
+        <is>
+          <t>Various US universities</t>
+        </is>
+      </c>
+      <c r="E166" s="64" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F166" s="64" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G166" s="64" t="inlineStr">
+        <is>
+          <t>URGENT - 24 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H166" s="64" t="inlineStr">
+        <is>
+          <t>Full or partial: tuition + stipend (varies by fellowship type)</t>
+        </is>
+      </c>
+      <c r="I166" s="64" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J166" s="64" t="inlineStr">
+        <is>
+          <t>TOEFL/IELTS (institution standard)</t>
+        </is>
+      </c>
+      <c r="K166" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L166" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N166" s="64" t="inlineStr">
+        <is>
+          <t>All fields</t>
+        </is>
+      </c>
+      <c r="O166" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P166" s="64" t="inlineStr">
+        <is>
+          <t>Restricted to women applicants; Kenya eligible; long-running American Association of University Women programme | LIVE-VERIFIED 2026-08-24: CONFIRMED: applications opened 17 Aug 2026, deadline 17 Sept 2026, 5pm ET. Programme must start on or before 15 Sept 2027.</t>
+        </is>
+      </c>
+      <c r="Q166" s="64" t="inlineStr">
+        <is>
+          <t>https://www.aauw.org/resources/programs/fellowships-grants/</t>
+        </is>
+      </c>
+      <c r="R166" s="65" t="inlineStr">
+        <is>
+          <t>Global - Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="64" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" s="64" t="inlineStr">
+        <is>
+          <t>Zonta International Amelia Earhart Fellowship</t>
+        </is>
+      </c>
+      <c r="C167" s="64" t="inlineStr">
+        <is>
+          <t>PhD in aerospace-related sciences and engineering (women only)</t>
+        </is>
+      </c>
+      <c r="D167" s="64" t="inlineStr">
+        <is>
+          <t>Various universities worldwide</t>
+        </is>
+      </c>
+      <c r="E167" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F167" s="64" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="G167" s="64" t="inlineStr">
+        <is>
+          <t>OPEN NOW - 83 DAYS REMAINING</t>
+        </is>
+      </c>
+      <c r="H167" s="64" t="inlineStr">
+        <is>
+          <t>Award: USD 10,000 (partial support)</t>
+        </is>
+      </c>
+      <c r="I167" s="64" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J167" s="64" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="K167" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L167" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N167" s="64" t="inlineStr">
+        <is>
+          <t>Aerospace Engineering / Space Sciences (women only)</t>
+        </is>
+      </c>
+      <c r="O167" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P167" s="64" t="inlineStr">
+        <is>
+          <t>Restricted to women pursuing PhD; niche field (aerospace); Kenya eligible as open international competition | LIVE-VERIFIED 2026-08-24: CONFIRMED: deadline for current fellowship cycle is 15 November 2026. Check zonta.org/AEFellowship for exact application portal opening.</t>
+        </is>
+      </c>
+      <c r="Q167" s="64" t="inlineStr">
+        <is>
+          <t>https://www.zonta.org/Web/Programs/Amelia_Earhart_Fellowship/</t>
+        </is>
+      </c>
+      <c r="R167" s="65" t="inlineStr">
+        <is>
+          <t>Global - Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="64" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" s="64" t="inlineStr">
+        <is>
+          <t>Schlumberger Foundation Faculty for the Future</t>
+        </is>
+      </c>
+      <c r="C168" s="64" t="inlineStr">
+        <is>
+          <t>PhD in STEM fields at top international universities (women only, from developing countries)</t>
+        </is>
+      </c>
+      <c r="D168" s="64" t="inlineStr">
+        <is>
+          <t>Selected top-ranked universities worldwide</t>
+        </is>
+      </c>
+      <c r="E168" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F168" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G168" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H168" s="64" t="inlineStr">
+        <is>
+          <t>Full: tuition + stipend + travel</t>
+        </is>
+      </c>
+      <c r="I168" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J168" s="64" t="inlineStr">
+        <is>
+          <t>English (institution standard)</t>
+        </is>
+      </c>
+      <c r="K168" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L168" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N168" s="64" t="inlineStr">
+        <is>
+          <t>STEM -- Physical Sciences, Engineering, Mathematics, Computer Science</t>
+        </is>
+      </c>
+      <c r="O168" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P168" s="64" t="inlineStr">
+        <is>
+          <t>Restricted to women in STEM PhD programmes intending to return to teach in home country; Kenya explicitly eligible; highly relevant for African women engineers | LIVE-VERIFIED 2026-08-24: Most recent confirmed deadline (2026-2027 cycle) was 7 Nov 2025, already closed. Next cycle (2027-2028) not yet announced -- historically opens around Aug-Sep with deadline Oct-Nov. Monitor fftf.slb.com.</t>
+        </is>
+      </c>
+      <c r="Q168" s="64" t="inlineStr">
+        <is>
+          <t>https://facultyforthefuture.net</t>
+        </is>
+      </c>
+      <c r="R168" s="65" t="inlineStr">
+        <is>
+          <t>Global - Sciences</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="64" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" s="64" t="inlineStr">
+        <is>
+          <t>GREAT Scholarships (British Council)</t>
+        </is>
+      </c>
+      <c r="C169" s="64" t="inlineStr">
+        <is>
+          <t>Masters at partner UK universities (country-specific allocation)</t>
+        </is>
+      </c>
+      <c r="D169" s="64" t="inlineStr">
+        <is>
+          <t>Various UK universities (partner list varies by year)</t>
+        </is>
+      </c>
+      <c r="E169" s="64" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F169" s="64" t="inlineStr">
+        <is>
+          <t>Check website (varies by partner university)</t>
+        </is>
+      </c>
+      <c r="G169" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H169" s="64" t="inlineStr">
+        <is>
+          <t>Full or partial: GBP 10,000+ tuition contribution (varies by university)</t>
+        </is>
+      </c>
+      <c r="I169" s="64" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J169" s="64" t="inlineStr">
+        <is>
+          <t>IELTS 6.5+</t>
+        </is>
+      </c>
+      <c r="K169" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L169" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N169" s="64" t="inlineStr">
+        <is>
+          <t>Varies by partner university and year</t>
+        </is>
+      </c>
+      <c r="O169" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P169" s="64" t="inlineStr">
+        <is>
+          <t>British Council programme; country allocation changes annually -- verify whether Kenya is on the current year's eligible country list before applying | LIVE-VERIFIED 2026-08-24: CONFIRMED: Kenya IS on the eligible country list for the 2026-27 cycle (confirmed via study-uk.britishcouncil.org/scholarships-funding/great-scholarships/kenya). GBP 10,000+ towards one-year taught postgraduate tuition at 60 partner UK universities. Deadlines set individually by each partner university, typically Jan-Jun for Sept entry.</t>
+        </is>
+      </c>
+      <c r="Q169" s="64" t="inlineStr">
+        <is>
+          <t>https://study-uk.britishcouncil.org/scholarships/great-scholarships</t>
+        </is>
+      </c>
+      <c r="R169" s="65" t="inlineStr">
+        <is>
+          <t>Global - Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="64" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" s="64" t="inlineStr">
+        <is>
+          <t>L'Oreal-UNESCO For Women in Science Fellowship</t>
+        </is>
+      </c>
+      <c r="C170" s="64" t="inlineStr">
+        <is>
+          <t>PhD or postdoctoral fellowship in life/physical sciences (women only)</t>
+        </is>
+      </c>
+      <c r="D170" s="64" t="inlineStr">
+        <is>
+          <t>Home institution or international host</t>
+        </is>
+      </c>
+      <c r="E170" s="64" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="F170" s="64" t="inlineStr">
+        <is>
+          <t>Check website</t>
+        </is>
+      </c>
+      <c r="G170" s="64" t="inlineStr">
+        <is>
+          <t>CHECK WEBSITE</t>
+        </is>
+      </c>
+      <c r="H170" s="64" t="inlineStr">
+        <is>
+          <t>Fellowship award (varies by region -- Sub-Saharan Africa programme exists)</t>
+        </is>
+      </c>
+      <c r="I170" s="64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J170" s="64" t="inlineStr">
+        <is>
+          <t>English or French</t>
+        </is>
+      </c>
+      <c r="K170" s="64" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="L170" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N170" s="64" t="inlineStr">
+        <is>
+          <t>Life Sciences / Physical Sciences / Engineering (women only)</t>
+        </is>
+      </c>
+      <c r="O170" s="64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P170" s="64" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa regional programme exists specifically; Kenya eligible; supports women researchers at PhD and postdoc level | LIVE-VERIFIED 2026-08-24: Most recent confirmed Sub-Saharan Africa deadline was 17 April 2026, already closed. Next cycle deadline not yet announced -- historically opens Feb-Mar. Monitor forwomeninscience.com/authority/sub-saharan-africa---regional-program.</t>
+        </is>
+      </c>
+      <c r="Q170" s="64" t="inlineStr">
+        <is>
+          <t>https://www.forwomeninscience.com</t>
+        </is>
+      </c>
+      <c r="R170" s="65" t="inlineStr">
         <is>
           <t>Global - Sciences</t>
         </is>
